--- a/portfolios.xlsx
+++ b/portfolios.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FFC804D-6185-4F0F-B0B2-B671D1F58D18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\jjnanthakumar.github.io\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C877B5D1-BAD5-48D0-BA25-04EA207C46BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certifications" sheetId="1" r:id="rId1"/>
@@ -27,7 +32,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="325">
   <si>
     <t>Title</t>
   </si>
@@ -1004,6 +1008,12 @@
   </si>
   <si>
     <t>images/piblitz.jpg</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>Currently Working on Azure Migration, Azure Synapse Solution and Django Web Application.</t>
   </si>
 </sst>
 </file>
@@ -1576,15 +1586,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G85"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="65.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="65.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.44140625" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="102" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" style="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -3616,28 +3626,28 @@
     <hyperlink ref="E74" r:id="rId8" xr:uid="{D9C0C981-CB38-4235-A77B-7B73A8D1355B}"/>
     <hyperlink ref="E75" r:id="rId9" xr:uid="{256B4442-C33A-484D-A51A-03B0A68C0D1A}"/>
     <hyperlink ref="E76" r:id="rId10" xr:uid="{11511F3E-24A6-40DC-8710-D6F763ABC7D0}"/>
-    <hyperlink ref="E68" r:id="rId11" xr:uid="{23538072-30C4-4325-A871-9979C940114B}"/>
-    <hyperlink ref="E69" r:id="rId12" xr:uid="{92658253-7FDE-4177-9BB5-57ABBEC11707}"/>
-    <hyperlink ref="E67" r:id="rId13" xr:uid="{760F6237-ED74-4C76-921F-A92DB49AA851}"/>
+    <hyperlink ref="E68" r:id="rId11" display="https://www.hackerrank.com/certificates/2766975846a6" xr:uid="{23538072-30C4-4325-A871-9979C940114B}"/>
+    <hyperlink ref="E69" r:id="rId12" display="https://www.hackerrank.com/certificates/1140c95b9b14" xr:uid="{92658253-7FDE-4177-9BB5-57ABBEC11707}"/>
+    <hyperlink ref="E67" r:id="rId13" display="https://www.hackerrank.com/certificates/867daffabda4" xr:uid="{760F6237-ED74-4C76-921F-A92DB49AA851}"/>
     <hyperlink ref="E40" r:id="rId14" xr:uid="{BE109821-CCDD-4A04-981A-9F6EFC5839F3}"/>
-    <hyperlink ref="E38" r:id="rId15" xr:uid="{193C03FB-8BC6-4219-AB14-ECE3411E93FC}"/>
+    <hyperlink ref="E38" r:id="rId15" display="https://www.hackerrank.com/certificates/3af4ddb28fab" xr:uid="{193C03FB-8BC6-4219-AB14-ECE3411E93FC}"/>
     <hyperlink ref="E35" r:id="rId16" xr:uid="{C4C48324-FD2D-4D60-97F7-1C543194CDA1}"/>
     <hyperlink ref="E34" r:id="rId17" xr:uid="{24CD5469-5A68-4595-8905-E3195BAA26D6}"/>
-    <hyperlink ref="E33" r:id="rId18" xr:uid="{4E5A9F5D-377D-4813-82DA-653909A03F55}"/>
+    <hyperlink ref="E33" r:id="rId18" display="https://www.hackerrank.com/certificates/6730cf1d0f21" xr:uid="{4E5A9F5D-377D-4813-82DA-653909A03F55}"/>
     <hyperlink ref="E32" r:id="rId19" xr:uid="{13330E2D-247C-4D68-B3A4-25AEC2481299}"/>
     <hyperlink ref="E13" r:id="rId20" xr:uid="{104CE576-4E8E-4A67-852D-469446BC152A}"/>
     <hyperlink ref="E10" r:id="rId21" xr:uid="{F5B1676B-40C2-41E4-8A7C-EE0DDF96B5AB}"/>
     <hyperlink ref="E11" r:id="rId22" xr:uid="{CF1353C0-1B68-45EB-B9D3-B3815B4819F9}"/>
     <hyperlink ref="E12" r:id="rId23" xr:uid="{C08302DF-FF6D-47C0-8C56-3AB13A011040}"/>
-    <hyperlink ref="E14" r:id="rId24" xr:uid="{D327F964-4247-480C-ABF2-CE1C58A5C248}"/>
+    <hyperlink ref="E14" r:id="rId24" display="https://olympus1.greatlearning.in/course_certificate/UAEGKOSB" xr:uid="{D327F964-4247-480C-ABF2-CE1C58A5C248}"/>
     <hyperlink ref="E18" r:id="rId25" xr:uid="{899ABF8F-A4FE-4A5E-81D4-FDAA431DAB0E}"/>
-    <hyperlink ref="E23" r:id="rId26" xr:uid="{DE2CBB3E-53B4-4A72-B17A-95F8DC50A680}"/>
-    <hyperlink ref="E26" r:id="rId27" xr:uid="{5873F399-7F29-4029-A2AF-C59477D7EEFA}"/>
-    <hyperlink ref="E27" r:id="rId28" xr:uid="{9CE1A66B-C3BE-475F-9AAC-35D820A2B426}"/>
-    <hyperlink ref="E28" r:id="rId29" xr:uid="{5442A54E-DEC1-418C-88C0-D3881C3E7DF7}"/>
-    <hyperlink ref="E24" r:id="rId30" xr:uid="{03797E5A-D7A7-48A4-A1B4-62A5C7C463AF}"/>
-    <hyperlink ref="E25" r:id="rId31" xr:uid="{0492AAD8-A54A-4838-943A-8F8C8C981536}"/>
-    <hyperlink ref="E30" r:id="rId32" xr:uid="{D163DA80-AE56-4D17-80D1-BCE62B9B0E77}"/>
+    <hyperlink ref="E23" r:id="rId26" display="https://www.hackerrank.com/certificates/cf58231a440f" xr:uid="{DE2CBB3E-53B4-4A72-B17A-95F8DC50A680}"/>
+    <hyperlink ref="E26" r:id="rId27" display="https://verify.greatlearning.in/SSMRYOWJ" xr:uid="{5873F399-7F29-4029-A2AF-C59477D7EEFA}"/>
+    <hyperlink ref="E27" r:id="rId28" display="https://verify.greatlearning.in/ZYQTXTJA" xr:uid="{9CE1A66B-C3BE-475F-9AAC-35D820A2B426}"/>
+    <hyperlink ref="E28" r:id="rId29" display="https://verify.greatlearning.in/GQGRZFQQ" xr:uid="{5442A54E-DEC1-418C-88C0-D3881C3E7DF7}"/>
+    <hyperlink ref="E24" r:id="rId30" display="https://www.hackerrank.com/certificates/4490b4a0e606" xr:uid="{03797E5A-D7A7-48A4-A1B4-62A5C7C463AF}"/>
+    <hyperlink ref="E25" r:id="rId31" display="https://www.hackerrank.com/certificates/fdeeaad81310" xr:uid="{0492AAD8-A54A-4838-943A-8F8C8C981536}"/>
+    <hyperlink ref="E30" r:id="rId32" display="https://www.hackerrank.com/certificates/1cadc360a79d" xr:uid="{D163DA80-AE56-4D17-80D1-BCE62B9B0E77}"/>
     <hyperlink ref="E36" r:id="rId33" xr:uid="{7EB46669-C518-425D-8A3E-395F05BE96F4}"/>
     <hyperlink ref="E56" r:id="rId34" xr:uid="{E604A0FD-1B8B-4069-A5D9-749A14F9519E}"/>
     <hyperlink ref="E57" r:id="rId35" xr:uid="{6D72DCB3-71D9-4096-B636-A24037DEC0A0}"/>
@@ -3665,16 +3675,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7494C2C-9786-4889-8081-3FC41A1A3B3E}">
   <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="112.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="112.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.42578125" customWidth="1"/>
-    <col min="9" max="9" width="107.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" customWidth="1"/>
+    <col min="9" max="9" width="107.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3711,10 +3721,10 @@
         <v>232</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>233</v>
+        <v>323</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>234</v>
+        <v>324</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>235</v>
@@ -3723,7 +3733,7 @@
         <v>236</v>
       </c>
       <c r="F2" s="27">
-        <v>44470</v>
+        <v>44652</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>236</v>
@@ -3738,22 +3748,22 @@
         <v>232</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D3" s="25" t="s">
         <v>235</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F3" s="27">
-        <v>44378</v>
+        <v>44470</v>
       </c>
       <c r="G3" s="27">
-        <v>44469</v>
+        <v>44651</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>237</v>
@@ -3765,10 +3775,10 @@
         <v>232</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D4" s="25" t="s">
         <v>235</v>
@@ -3777,77 +3787,75 @@
         <v>240</v>
       </c>
       <c r="F4" s="20">
-        <v>44263</v>
+        <v>44378</v>
       </c>
       <c r="G4" s="20">
-        <v>44377</v>
+        <v>44469</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>237</v>
       </c>
       <c r="I4" s="5"/>
     </row>
-    <row r="5" spans="1:9" s="33" customFormat="1" ht="75">
-      <c r="A5" s="28" t="s">
+    <row r="5" spans="1:9" s="33" customFormat="1">
+      <c r="A5" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="20">
+        <v>44263</v>
+      </c>
+      <c r="G5" s="20">
+        <v>44377</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="57.6">
+      <c r="A6" s="28" t="s">
         <v>243</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B6" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C6" s="29" t="s">
         <v>245</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D6" s="30" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E6" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F6" s="31">
         <v>44137</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G6" s="31">
         <v>44200</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H6" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="I5" s="32" t="s">
+      <c r="I6" s="32" t="s">
         <v>246</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="5" t="s">
-        <v>247</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F6" s="20">
-        <v>44136</v>
-      </c>
-      <c r="G6" s="20">
-        <v>44166</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>248</v>
@@ -3862,57 +3870,75 @@
         <v>240</v>
       </c>
       <c r="F7" s="20">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="G7" s="20">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>237</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>240</v>
       </c>
       <c r="F8" s="20">
-        <v>43432</v>
+        <v>44105</v>
       </c>
       <c r="G8" s="20">
-        <v>43442</v>
+        <v>44136</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>237</v>
       </c>
       <c r="I8" s="6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>255</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="F9" s="27">
+        <v>43432</v>
+      </c>
+      <c r="G9" s="27">
+        <v>43442</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="5"/>
@@ -3949,15 +3975,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:I8" xr:uid="{B7494C2C-9786-4889-8081-3FC41A1A3B3E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I8">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I9">
       <sortCondition descending="1" ref="F1:F8"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="I5" r:id="rId1" xr:uid="{F023270F-32A2-4084-BC0C-759F75126131}"/>
-    <hyperlink ref="I6" r:id="rId2" xr:uid="{36657B35-2DE3-4353-875D-05EDE8EC8328}"/>
-    <hyperlink ref="I7" r:id="rId3" xr:uid="{424F7718-10F0-4367-9C1C-C1FF49F2EBFA}"/>
-    <hyperlink ref="I8" r:id="rId4" xr:uid="{004196DD-DF68-41F8-8E08-7FF73A789B6A}"/>
+    <hyperlink ref="I6" r:id="rId1" xr:uid="{F023270F-32A2-4084-BC0C-759F75126131}"/>
+    <hyperlink ref="I7" r:id="rId2" xr:uid="{36657B35-2DE3-4353-875D-05EDE8EC8328}"/>
+    <hyperlink ref="I8" r:id="rId3" xr:uid="{424F7718-10F0-4367-9C1C-C1FF49F2EBFA}"/>
+    <hyperlink ref="I9" r:id="rId4" xr:uid="{004196DD-DF68-41F8-8E08-7FF73A789B6A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3966,10 +3992,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718451B2-E12D-4ABD-B26C-5975AED3964E}">
   <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -4017,7 +4043,7 @@
         <v>263</v>
       </c>
       <c r="B6" s="7">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4041,7 +4067,7 @@
         <v>266</v>
       </c>
       <c r="B9" s="7">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4057,7 +4083,7 @@
         <v>268</v>
       </c>
       <c r="B11" s="7">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4065,7 +4091,7 @@
         <v>269</v>
       </c>
       <c r="B12" s="7">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4089,7 +4115,7 @@
         <v>272</v>
       </c>
       <c r="B15" s="7">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4169,12 +4195,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4DB9CC9-BE76-4E73-A91C-99466DD45DAE}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="74.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="74.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -4394,9 +4420,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4617,22 +4646,43 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F92213D-1611-4A06-8F7F-2A2F3FD54BB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E4A532-34F4-4909-9773-2D1B4D74CA0C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7B86EC6-7D1E-4865-AE9C-08032C03144E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7B86EC6-7D1E-4865-AE9C-08032C03144E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="0fefa867-d15f-4a0d-9945-ea6297accf67"/>
+    <ds:schemaRef ds:uri="fadb6cc6-1edc-4022-b9cc-b0c463f8d195"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E4A532-34F4-4909-9773-2D1B4D74CA0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F92213D-1611-4A06-8F7F-2A2F3FD54BB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/portfolios.xlsx
+++ b/portfolios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\jjnanthakumar.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C877B5D1-BAD5-48D0-BA25-04EA207C46BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF09141-ADB0-4031-9623-989E315E424A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certifications" sheetId="1" r:id="rId1"/>
@@ -3757,7 +3757,7 @@
         <v>235</v>
       </c>
       <c r="E3" s="25" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F3" s="27">
         <v>44470</v>
@@ -4420,12 +4420,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4646,15 +4643,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E4A532-34F4-4909-9773-2D1B4D74CA0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F92213D-1611-4A06-8F7F-2A2F3FD54BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4679,10 +4680,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F92213D-1611-4A06-8F7F-2A2F3FD54BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E4A532-34F4-4909-9773-2D1B4D74CA0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/portfolios.xlsx
+++ b/portfolios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\jjnanthakumar.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF09141-ADB0-4031-9623-989E315E424A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02A9A82-1BD7-4B96-8DF8-F59B30D051EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certifications" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,9 @@
     <sheet name="Projects" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Certifications!$A$1:$G$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Certifications!$A$1:$G$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Experience!$A$1:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Skills!$A$1:$B$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Skills!$A$1:$B$21</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="328">
   <si>
     <t>Title</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Microsoft</t>
   </si>
   <si>
-    <t>1095-4728</t>
-  </si>
-  <si>
     <t>https://www.credly.com/badges/de23617e-5bbf-4da8-bd33-9025ba84933a/public_url</t>
   </si>
   <si>
@@ -158,9 +155,6 @@
     <t>H953-9167</t>
   </si>
   <si>
-    <t>https://www.credly.com/badges/5b471ed6-57b5-466c-9d5c-654d5f5debca?source=linked_in_profile</t>
-  </si>
-  <si>
     <t>Python for Beginners</t>
   </si>
   <si>
@@ -833,9 +827,6 @@
     <t>JAVA SCRIPT</t>
   </si>
   <si>
-    <t>SQL DATABASE</t>
-  </si>
-  <si>
     <t>TKINTER</t>
   </si>
   <si>
@@ -878,9 +869,6 @@
     <t>POWER AUTOMATE</t>
   </si>
   <si>
-    <t>POWER BI</t>
-  </si>
-  <si>
     <t>AZURE</t>
   </si>
   <si>
@@ -1014,6 +1002,27 @@
   </si>
   <si>
     <t>Currently Working on Azure Migration, Azure Synapse Solution and Django Web Application.</t>
+  </si>
+  <si>
+    <t>I340-8441</t>
+  </si>
+  <si>
+    <t>Microsoft Certified: DevOps Engineer Expert</t>
+  </si>
+  <si>
+    <t>I365-1183</t>
+  </si>
+  <si>
+    <t>https://www.credly.com/badges/20ccf763-1844-43c2-a3bf-8571422339e1?source=jjnanthakumar.github.io</t>
+  </si>
+  <si>
+    <t>https://www.credly.com/badges/5b471ed6-57b5-466c-9d5c-654d5f5debca?jjnanthakumar.github.io</t>
+  </si>
+  <si>
+    <t>July 22, 2022</t>
+  </si>
+  <si>
+    <t>SQL</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1089,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1188,12 +1197,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1214,9 +1238,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1261,15 +1282,34 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1585,7 +1625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="65.5546875" bestFit="1" customWidth="1"/>
@@ -1594,1185 +1634,1184 @@
     <col min="4" max="4" width="40.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="102" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.109375" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="48" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="49" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="54" t="s">
+        <v>322</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="54" t="s">
+        <v>323</v>
+      </c>
+      <c r="E2" s="55" t="s">
+        <v>324</v>
+      </c>
+      <c r="F2" s="52">
+        <v>0.92</v>
+      </c>
+      <c r="G2" s="56" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D3" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F3" s="52">
+        <v>0.85</v>
+      </c>
+      <c r="G3" s="53">
+        <v>44560</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7">
-        <v>0.85</v>
-      </c>
-      <c r="G2" s="20">
-        <v>44560</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="5" t="s">
+      <c r="B4" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="E4" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="52">
+        <v>1</v>
+      </c>
+      <c r="G4" s="53">
+        <v>44552</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C5" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7">
-        <v>1</v>
-      </c>
-      <c r="G3" s="20">
-        <v>44552</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="39" t="s">
+      <c r="D5" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="39" t="s">
+      <c r="E5" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="47" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="41">
+      <c r="F5" s="40">
         <v>0.98</v>
       </c>
-      <c r="G4" s="40">
+      <c r="G5" s="26">
         <v>44527</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="34" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D5)</f>
-        <v>https://www.hackerrank.com/certificates/524e499db551</v>
-      </c>
-      <c r="F5" s="13">
-        <v>1</v>
-      </c>
-      <c r="G5" s="21">
-        <v>44493</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="33" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D6)</f>
+        <v>https://www.hackerrank.com/certificates/524e499db551</v>
+      </c>
+      <c r="F6" s="13">
+        <v>1</v>
+      </c>
+      <c r="G6" s="26">
+        <v>44493</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="E7" s="33" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D7)</f>
+        <v>https://www.hackerrank.com/certificates/7a872682b210</v>
+      </c>
+      <c r="F7" s="13">
+        <v>1</v>
+      </c>
+      <c r="G7" s="39">
+        <v>44490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="34" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D6)</f>
-        <v>https://www.hackerrank.com/certificates/7a872682b210</v>
-      </c>
-      <c r="F6" s="13">
-        <v>1</v>
-      </c>
-      <c r="G6" s="21">
-        <v>44490</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="5" t="s">
+      <c r="B8" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="5" t="s">
+      <c r="E8" s="51" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D8)</f>
+        <v>https://www.hackerrank.com/certificates/eafe133d26dc</v>
+      </c>
+      <c r="F8" s="52">
+        <v>1</v>
+      </c>
+      <c r="G8" s="53">
+        <v>44469</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D7)</f>
-        <v>https://www.hackerrank.com/certificates/eafe133d26dc</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="20">
-        <v>44469</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="39" t="s">
+      <c r="B9" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="39" t="s">
+      <c r="E9" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="47" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="41">
+      <c r="F9" s="40">
         <v>0.94</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G9" s="26">
         <v>44439</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="13">
-        <v>1</v>
-      </c>
-      <c r="G9" s="21">
-        <v>44419</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="13">
+        <v>1</v>
+      </c>
+      <c r="G10" s="26">
+        <v>44419</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="12" t="s">
+      <c r="E11" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="34" t="s">
+      <c r="F11" s="13">
+        <v>1</v>
+      </c>
+      <c r="G11" s="39">
+        <v>44418</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="13">
-        <v>1</v>
-      </c>
-      <c r="G10" s="21">
+      <c r="B12" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="52">
+        <v>1</v>
+      </c>
+      <c r="G12" s="53">
         <v>44418</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="6" t="s">
+    <row r="13" spans="1:7">
+      <c r="A13" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="7">
-        <v>1</v>
-      </c>
-      <c r="G11" s="20">
-        <v>44418</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="25" t="s">
+      <c r="B13" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="36">
+      <c r="E13" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="F13" s="35">
         <v>0.88</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G13" s="26">
         <v>44412</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="7">
-        <v>1</v>
-      </c>
-      <c r="G13" s="20">
-        <v>44388</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="6" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D14)</f>
-        <v>https://verify.greatlearning.in/UAEGKOSB</v>
+        <v>39</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="F14" s="7">
         <v>1</v>
       </c>
-      <c r="G14" s="20">
-        <v>44348</v>
+      <c r="G14" s="19">
+        <v>44388</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="12" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E15" s="6" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D15)</f>
-        <v>https://ude.my/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707</v>
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D15)</f>
+        <v>https://verify.greatlearning.in/UAEGKOSB</v>
       </c>
       <c r="F15" s="13">
         <v>1</v>
       </c>
-      <c r="G15" s="21">
-        <v>44346</v>
+      <c r="G15" s="20">
+        <v>44348</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="E16" s="34" t="str">
+        <v>47</v>
+      </c>
+      <c r="E16" s="33" t="str">
         <f>HYPERLINK("https://ude.my/"&amp; D16)</f>
-        <v>https://ude.my/UC-a3ba46b5-170d-4510-a813-c3dff69a6697</v>
+        <v>https://ude.my/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707</v>
       </c>
       <c r="F16" s="13">
         <v>1</v>
       </c>
-      <c r="G16" s="21">
-        <v>44339</v>
+      <c r="G16" s="20">
+        <v>44346</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E17" s="6" t="str">
         <f>HYPERLINK("https://ude.my/"&amp; D17)</f>
-        <v>https://ude.my/UC-6ee1aa7b-93ad-4437-ac78-fb96957a2f3b</v>
+        <v>https://ude.my/UC-a3ba46b5-170d-4510-a813-c3dff69a6697</v>
       </c>
       <c r="F17" s="7">
         <v>1</v>
       </c>
-      <c r="G17" s="20">
-        <v>44332</v>
+      <c r="G17" s="19">
+        <v>44339</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="E18" s="6" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D18)</f>
+        <v>https://ude.my/UC-6ee1aa7b-93ad-4437-ac78-fb96957a2f3b</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
       </c>
-      <c r="G18" s="20">
-        <v>44312</v>
+      <c r="G18" s="19">
+        <v>44332</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="6" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D19)</f>
+        <v>56</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="19">
+        <v>44312</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="34" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D20)</f>
         <v>https://ude.my/UC-c9ca1de5-ac7a-449c-923d-aa727cbd1906</v>
       </c>
-      <c r="F19" s="7">
-        <v>1</v>
-      </c>
-      <c r="G19" s="20">
+      <c r="F20" s="35">
+        <v>1</v>
+      </c>
+      <c r="G20" s="26">
         <v>44312</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D20" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20" s="35" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D20)</f>
-        <v>https://ude.my/UC-b2d528a0-beba-44fc-96bb-c1ccd88ee68a</v>
-      </c>
-      <c r="F20" s="36">
-        <v>1</v>
-      </c>
-      <c r="G20" s="27">
-        <v>44309</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E21" s="6" t="str">
         <f>HYPERLINK("https://ude.my/"&amp; D21)</f>
-        <v>https://ude.my/UC-1f46a0d1-37f4-4a8c-95f6-839311438ab7</v>
+        <v>https://ude.my/UC-b2d528a0-beba-44fc-96bb-c1ccd88ee68a</v>
       </c>
       <c r="F21" s="13">
         <v>1</v>
       </c>
-      <c r="G21" s="21">
-        <v>44306</v>
+      <c r="G21" s="20">
+        <v>44309</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="12" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="E22" s="34" t="str">
+        <v>65</v>
+      </c>
+      <c r="E22" s="33" t="str">
         <f>HYPERLINK("https://ude.my/"&amp; D22)</f>
-        <v>https://ude.my/UC-18dd832f-d345-44f1-92cf-281f71e773d1</v>
+        <v>https://ude.my/UC-1f46a0d1-37f4-4a8c-95f6-839311438ab7</v>
       </c>
       <c r="F22" s="13">
         <v>1</v>
       </c>
-      <c r="G22" s="21">
-        <v>44300</v>
+      <c r="G22" s="20">
+        <v>44306</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E23" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D23)</f>
-        <v>https://www.hackerrank.com/certificates/cf58231a440f</v>
+        <f>HYPERLINK("https://ude.my/"&amp; D23)</f>
+        <v>https://ude.my/UC-18dd832f-d345-44f1-92cf-281f71e773d1</v>
       </c>
       <c r="F23" s="7">
         <v>1</v>
       </c>
-      <c r="G23" s="20">
-        <v>44288</v>
+      <c r="G23" s="19">
+        <v>44300</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E24" s="6" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D24)</f>
-        <v>https://www.hackerrank.com/certificates/4490b4a0e606</v>
+        <v>https://www.hackerrank.com/certificates/cf58231a440f</v>
       </c>
       <c r="F24" s="7">
         <v>1</v>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="19">
         <v>44288</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="5" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E25" s="6" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D25)</f>
+        <v>https://www.hackerrank.com/certificates/4490b4a0e606</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1</v>
+      </c>
+      <c r="G25" s="19">
+        <v>44288</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="34" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D26)</f>
         <v>https://www.hackerrank.com/certificates/fdeeaad81310</v>
       </c>
-      <c r="F25" s="7">
-        <v>1</v>
-      </c>
-      <c r="G25" s="20">
+      <c r="F26" s="35">
+        <v>1</v>
+      </c>
+      <c r="G26" s="26">
         <v>44288</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D26" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="35" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D26)</f>
+    <row r="27" spans="1:7">
+      <c r="A27" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="34" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D27)</f>
         <v>https://verify.greatlearning.in/SSMRYOWJ</v>
       </c>
-      <c r="F26" s="36">
-        <v>1</v>
-      </c>
-      <c r="G26" s="27">
-        <v>44287</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="35" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D27)</f>
-        <v>https://verify.greatlearning.in/ZYQTXTJA</v>
-      </c>
-      <c r="F27" s="41">
-        <v>1</v>
-      </c>
-      <c r="G27" s="40">
+      <c r="F27" s="40">
+        <v>1</v>
+      </c>
+      <c r="G27" s="39">
         <v>44287</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="5" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B28" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E28" s="6" t="str">
         <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D28)</f>
-        <v>https://verify.greatlearning.in/GQGRZFQQ</v>
+        <v>https://verify.greatlearning.in/ZYQTXTJA</v>
       </c>
       <c r="F28" s="13">
         <v>1</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="20">
         <v>44287</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E29" s="6" t="str">
         <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D29)</f>
-        <v>https://verify.greatlearning.in/HSNELKCZ</v>
+        <v>https://verify.greatlearning.in/GQGRZFQQ</v>
       </c>
       <c r="F29" s="13">
         <v>1</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="19">
         <v>44287</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E30" s="34" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D30)</f>
-        <v>https://www.hackerrank.com/certificates/1cadc360a79d</v>
+        <v>82</v>
+      </c>
+      <c r="E30" s="33" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D30)</f>
+        <v>https://verify.greatlearning.in/HSNELKCZ</v>
       </c>
       <c r="F30" s="13">
         <v>1</v>
       </c>
-      <c r="G30" s="21">
-        <v>44268</v>
+      <c r="G30" s="20">
+        <v>44287</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="6" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D31)</f>
+        <v>https://www.hackerrank.com/certificates/1cadc360a79d</v>
+      </c>
+      <c r="F31" s="7">
+        <v>1</v>
+      </c>
+      <c r="G31" s="19">
+        <v>44268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E31" s="6" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D31)</f>
+      <c r="E32" s="34" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D32)</f>
         <v>https://ude.my/UC-61e2521b-a9bb-48dc-bb44-3679ba047cf8</v>
       </c>
-      <c r="F31" s="7">
-        <v>1</v>
-      </c>
-      <c r="G31" s="20">
+      <c r="F32" s="35">
+        <v>1</v>
+      </c>
+      <c r="G32" s="26">
         <v>44249</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="B32" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="D32" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="F32" s="36">
-        <v>0.97</v>
-      </c>
-      <c r="G32" s="43">
-        <v>44246</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="5" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D33)</f>
-        <v>https://www.hackerrank.com/certificates/6730CF1D0F21</v>
+        <v>90</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="F33" s="7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="G33" s="17">
-        <v>44209</v>
+        <v>44246</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="5" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
+      </c>
+      <c r="E34" s="6" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D34)</f>
+        <v>https://www.hackerrank.com/certificates/6730CF1D0F21</v>
       </c>
       <c r="F34" s="7">
         <v>1</v>
       </c>
       <c r="G34" s="17">
-        <v>44180</v>
+        <v>44209</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="12" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="D35" s="44">
-        <v>271676</v>
+        <v>27</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="F35" s="13">
         <v>1</v>
       </c>
-      <c r="G35" s="19">
-        <v>44176</v>
+      <c r="G35" s="18">
+        <v>44180</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>101</v>
       </c>
       <c r="D36" s="8">
         <v>271676</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F36" s="7">
         <v>1</v>
       </c>
-      <c r="G36" s="21">
+      <c r="G36" s="18">
         <v>44176</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D37)</f>
-        <v>https://www.coursera.org/verify/3NB72YUYKWLV</v>
+        <v>99</v>
+      </c>
+      <c r="D37" s="8">
+        <v>271676</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="F37" s="7">
         <v>1</v>
       </c>
-      <c r="G37" s="19">
-        <v>44165</v>
+      <c r="G37" s="20">
+        <v>44176</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="5" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E38" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D38)</f>
-        <v>https://www.hackerrank.com/certificates/3AF4DDB28FAB</v>
+        <v>104</v>
+      </c>
+      <c r="E38" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D38)</f>
+        <v>https://www.coursera.org/verify/3NB72YUYKWLV</v>
       </c>
       <c r="F38" s="7">
         <v>1</v>
       </c>
-      <c r="G38" s="19">
-        <v>44146</v>
+      <c r="G38" s="18">
+        <v>44165</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="5" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E39" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D39)</f>
-        <v>https://www.coursera.org/verify/AW6A4NWBVJ9V</v>
+        <v>106</v>
+      </c>
+      <c r="E39" s="6" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D39)</f>
+        <v>https://www.hackerrank.com/certificates/3AF4DDB28FAB</v>
       </c>
       <c r="F39" s="7">
         <v>1</v>
       </c>
-      <c r="G39" s="19">
-        <v>44135</v>
+      <c r="G39" s="18">
+        <v>44146</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>116</v>
+        <v>109</v>
+      </c>
+      <c r="E40" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D40)</f>
+        <v>https://www.coursera.org/verify/AW6A4NWBVJ9V</v>
       </c>
       <c r="F40" s="7">
         <v>1</v>
       </c>
-      <c r="G40" s="19">
+      <c r="G40" s="18">
         <v>44135</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="12" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D41)</f>
-        <v>https://www.coursera.org/verify/3WQ6APAJLP9T</v>
+        <v>113</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="F41" s="7">
         <v>1</v>
       </c>
-      <c r="G41" s="19">
-        <v>44126</v>
+      <c r="G41" s="18">
+        <v>44135</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B42" s="12" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E42" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D42)</f>
-        <v>https://www.coursera.org/verify/8DZVQYMNERJA</v>
+        <v>https://www.coursera.org/verify/3WQ6APAJLP9T</v>
       </c>
       <c r="F42" s="16">
         <v>1</v>
       </c>
-      <c r="G42" s="19">
+      <c r="G42" s="18">
         <v>44126</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="5" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E43" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D43)</f>
-        <v>https://www.coursera.org/verify/specialization/LGGYURMTBUUG</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D43)</f>
+        <v>https://www.coursera.org/verify/8DZVQYMNERJA</v>
       </c>
       <c r="F43" s="16">
         <v>1</v>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="18">
         <v>44126</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="5" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E44" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D44)</f>
-        <v>https://www.coursera.org/verify/LVBJNAL79BLV</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D44)</f>
+        <v>https://www.coursera.org/verify/specialization/LGGYURMTBUUG</v>
       </c>
       <c r="F44" s="16">
-        <v>0.97</v>
-      </c>
-      <c r="G44" s="19">
-        <v>44124</v>
+        <v>1</v>
+      </c>
+      <c r="G44" s="18">
+        <v>44126</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="5" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E45" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D45)</f>
-        <v>https://www.coursera.org/verify/specialization/6NXPUFTEK3Z7</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D45)</f>
+        <v>https://www.coursera.org/verify/LVBJNAL79BLV</v>
       </c>
       <c r="F45" s="16">
-        <v>1</v>
-      </c>
-      <c r="G45" s="19">
+        <v>0.97</v>
+      </c>
+      <c r="G45" s="18">
         <v>44124</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E46" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D46)</f>
-        <v>https://www.coursera.org/verify/4XRSLQYDGXHF</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D46)</f>
+        <v>https://www.coursera.org/verify/specialization/6NXPUFTEK3Z7</v>
       </c>
       <c r="F46" s="16">
-        <v>0.98</v>
-      </c>
-      <c r="G46" s="19">
-        <v>44122</v>
+        <v>1</v>
+      </c>
+      <c r="G46" s="18">
+        <v>44124</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="5" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E47" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/account/accomplishments/certificate/" &amp; D47)</f>
-        <v>https://www.coursera.org/account/accomplishments/certificate/6KQ8S8U4FGQ5</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D47)</f>
+        <v>https://www.coursera.org/verify/4XRSLQYDGXHF</v>
       </c>
       <c r="F47" s="16">
-        <v>1</v>
-      </c>
-      <c r="G47" s="19">
+        <v>0.98</v>
+      </c>
+      <c r="G47" s="18">
         <v>44122</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="5" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E48" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D48)</f>
-        <v>https://www.coursera.org/verify/7JKY6ZQ9D76M</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/account/accomplishments/certificate/" &amp; D48)</f>
+        <v>https://www.coursera.org/account/accomplishments/certificate/6KQ8S8U4FGQ5</v>
       </c>
       <c r="F48" s="16">
         <v>1</v>
       </c>
-      <c r="G48" s="19">
-        <v>44112</v>
+      <c r="G48" s="18">
+        <v>44122</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="5" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E49" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D49)</f>
-        <v>https://www.coursera.org/verify/QWX8PHM4TZUF</v>
+        <v>https://www.coursera.org/verify/7JKY6ZQ9D76M</v>
       </c>
       <c r="F49" s="7">
         <v>1</v>
       </c>
-      <c r="G49" s="19">
-        <v>44105</v>
+      <c r="G49" s="18">
+        <v>44112</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="5" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E50" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D50)</f>
-        <v>https://www.coursera.org/verify/ARXP6JVNYNAM</v>
+        <v>https://www.coursera.org/verify/QWX8PHM4TZUF</v>
       </c>
       <c r="F50" s="7">
         <v>1</v>
@@ -2783,68 +2822,68 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="E51" s="6" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D51)</f>
-        <v>https://verify.greatlearning.in/UYEYVCWB</v>
+        <v>137</v>
+      </c>
+      <c r="E51" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D51)</f>
+        <v>https://www.coursera.org/verify/ARXP6JVNYNAM</v>
       </c>
       <c r="F51" s="7">
         <v>1</v>
       </c>
-      <c r="G51" s="20">
+      <c r="G51" s="17">
         <v>44105</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="12" t="s">
-        <v>31</v>
+        <v>136</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>131</v>
+        <v>42</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="E52" s="10" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D52)</f>
-        <v>https://www.coursera.org/verify/EUKYBKW2SUXX</v>
+        <v>138</v>
+      </c>
+      <c r="E52" s="33" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D52)</f>
+        <v>https://verify.greatlearning.in/UYEYVCWB</v>
       </c>
       <c r="F52" s="13">
         <v>1</v>
       </c>
-      <c r="G52" s="19">
-        <v>44104</v>
+      <c r="G52" s="20">
+        <v>44105</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="5" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E53" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D53)</f>
-        <v>https://www.coursera.org/verify/EUTL7GRT9ZQ4</v>
+        <v>https://www.coursera.org/verify/EUKYBKW2SUXX</v>
       </c>
       <c r="F53" s="7">
         <v>1</v>
@@ -2855,161 +2894,161 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>105</v>
+        <v>129</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E54" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D54)</f>
-        <v>https://www.coursera.org/verify/MX93X95TXB9V</v>
+        <v>https://www.coursera.org/verify/EUTL7GRT9ZQ4</v>
       </c>
       <c r="F54" s="13">
         <v>1</v>
       </c>
       <c r="G54" s="17">
-        <v>44080</v>
+        <v>44104</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="5" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>105</v>
+        <v>108</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E55" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D55)</f>
-        <v>https://www.coursera.org/verify/ERVJF5JMFDRV</v>
+        <v>https://www.coursera.org/verify/MX93X95TXB9V</v>
       </c>
       <c r="F55" s="13">
         <v>1</v>
       </c>
-      <c r="G55" s="20">
-        <v>44067</v>
+      <c r="G55" s="17">
+        <v>44080</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>151</v>
+        <v>103</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E56" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D56)</f>
+        <v>https://www.coursera.org/verify/ERVJF5JMFDRV</v>
       </c>
       <c r="F56" s="13">
         <v>1</v>
       </c>
-      <c r="G56" s="20">
-        <v>44066</v>
+      <c r="G56" s="19">
+        <v>44067</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B57" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E57" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="C57" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="F57" s="13">
         <v>1</v>
       </c>
-      <c r="G57" s="20">
+      <c r="G57" s="19">
         <v>44066</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="12" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D58" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="E58" s="34" t="s">
-        <v>155</v>
+        <v>147</v>
+      </c>
+      <c r="D58" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="E58" s="33" t="s">
+        <v>151</v>
       </c>
       <c r="F58" s="13">
         <v>1</v>
       </c>
-      <c r="G58" s="21">
+      <c r="G58" s="20">
         <v>44066</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E59" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D59)</f>
-        <v>https://www.coursera.org/verify/P53AV7SZHJ52</v>
+        <v>152</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="F59" s="7">
         <v>1</v>
       </c>
-      <c r="G59" s="17">
-        <v>44063</v>
+      <c r="G59" s="19">
+        <v>44066</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E60" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D60)</f>
-        <v>https://www.coursera.org/verify/specialization/FQXP3E6NT3YM</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D60)</f>
+        <v>https://www.coursera.org/verify/P53AV7SZHJ52</v>
       </c>
       <c r="F60" s="7">
         <v>1</v>
@@ -3020,212 +3059,212 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>124</v>
+        <v>156</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E61" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D61)</f>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D61)</f>
+        <v>https://www.coursera.org/verify/specialization/FQXP3E6NT3YM</v>
+      </c>
+      <c r="F61" s="7">
+        <v>1</v>
+      </c>
+      <c r="G61" s="17">
+        <v>44063</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B62" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="D62" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="E62" s="47" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D62)</f>
         <v>https://www.coursera.org/verify/MQ4NMBLXN3G6</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F62" s="40">
         <v>0.97</v>
       </c>
-      <c r="G61" s="17">
+      <c r="G62" s="41">
         <v>44056</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7">
-      <c r="A62" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="B62" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="C62" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="E62" s="51" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D62)</f>
-        <v>https://www.coursera.org/verify/UQ5RQLWBRLJA</v>
-      </c>
-      <c r="F62" s="41">
-        <v>0.96</v>
-      </c>
-      <c r="G62" s="42">
-        <v>44055</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="5" t="s">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>48</v>
+        <v>122</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E63" s="6" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D63)</f>
-        <v>https://ude.my/UC-57e2fe2c-3570-4bb3-862f-19b05a9b4413</v>
+        <v>161</v>
+      </c>
+      <c r="E63" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D63)</f>
+        <v>https://www.coursera.org/verify/UQ5RQLWBRLJA</v>
       </c>
       <c r="F63" s="13">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="G63" s="17">
-        <v>44054</v>
+        <v>44055</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>105</v>
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E64" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D64)</f>
-        <v>https://www.coursera.org/verify/HS9S3MQ9U8G5</v>
+        <v>162</v>
+      </c>
+      <c r="E64" s="6" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D64)</f>
+        <v>https://ude.my/UC-57e2fe2c-3570-4bb3-862f-19b05a9b4413</v>
       </c>
       <c r="F64" s="13">
         <v>1</v>
       </c>
       <c r="G64" s="17">
-        <v>44022</v>
+        <v>44054</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="12" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E65" s="10" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D65)</f>
-        <v>https://www.coursera.org/verify/Z27MPBY34D3J</v>
+        <v>https://www.coursera.org/verify/HS9S3MQ9U8G5</v>
       </c>
       <c r="F65" s="13">
         <v>1</v>
       </c>
-      <c r="G65" s="19">
-        <v>44021</v>
+      <c r="G65" s="18">
+        <v>44022</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="12" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E66" s="10" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D66)</f>
+        <v>https://www.coursera.org/verify/Z27MPBY34D3J</v>
+      </c>
+      <c r="F66" s="13">
+        <v>1</v>
+      </c>
+      <c r="G66" s="18">
+        <v>44021</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E67" s="10" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D67)</f>
         <v>https://www.coursera.org/verify/L4NCNJMVFQPU</v>
       </c>
-      <c r="F66" s="13">
-        <v>1</v>
-      </c>
-      <c r="G66" s="19">
+      <c r="F67" s="13">
+        <v>1</v>
+      </c>
+      <c r="G67" s="18">
         <v>44013</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D67" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="E67" s="10" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D67)</f>
-        <v>https://www.hackerrank.com/certificates/867DAFFABDA4</v>
-      </c>
-      <c r="F67" s="11">
-        <v>1</v>
-      </c>
-      <c r="G67" s="19">
-        <v>44004</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E68" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D68)</f>
-        <v>https://www.hackerrank.com/certificates/2766975846A6</v>
+        <v>https://www.hackerrank.com/certificates/867DAFFABDA4</v>
       </c>
       <c r="F68" s="11">
         <v>1</v>
       </c>
       <c r="G68" s="17">
-        <v>44003</v>
+        <v>44004</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E69" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D69)</f>
-        <v>https://www.hackerrank.com/certificates/1140C95B9B14</v>
+        <v>https://www.hackerrank.com/certificates/2766975846A6</v>
       </c>
       <c r="F69" s="11">
         <v>1</v>
@@ -3235,438 +3274,463 @@
       </c>
     </row>
     <row r="70" spans="1:7">
-      <c r="A70" s="5" t="s">
-        <v>31</v>
+      <c r="A70" s="2" t="s">
+        <v>173</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>177</v>
+        <v>17</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>174</v>
       </c>
       <c r="E70" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D70)</f>
-        <v>https://www.coursera.org/verify/WG7CRBWGK8FW</v>
-      </c>
-      <c r="F70" s="16">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D70)</f>
+        <v>https://www.hackerrank.com/certificates/1140C95B9B14</v>
+      </c>
+      <c r="F70" s="62">
         <v>1</v>
       </c>
       <c r="G70" s="17">
-        <v>43999</v>
+        <v>44003</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>105</v>
+        <v>30</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E71" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D71)</f>
-        <v>https://www.coursera.org/verify/L5XQHDFRBG5S</v>
+        <v>https://www.coursera.org/verify/WG7CRBWGK8FW</v>
       </c>
       <c r="F71" s="16">
-        <v>0.94</v>
+        <v>1</v>
       </c>
       <c r="G71" s="17">
-        <v>43995</v>
+        <v>43999</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="5" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E72" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D72)</f>
-        <v>https://www.coursera.org/verify/F6ASNEAAYVGZ</v>
+        <v>https://www.coursera.org/verify/L5XQHDFRBG5S</v>
       </c>
       <c r="F72" s="7">
         <v>0.94</v>
       </c>
       <c r="G72" s="17">
-        <v>43987</v>
+        <v>43995</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="5" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E73" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D73)</f>
+        <v>https://www.coursera.org/verify/F6ASNEAAYVGZ</v>
+      </c>
+      <c r="F73" s="7">
+        <v>0.94</v>
+      </c>
+      <c r="G73" s="17">
+        <v>43987</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E74" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D74)</f>
         <v>https://www.coursera.org/verify/3W45QQBKACKZ</v>
       </c>
-      <c r="F73" s="7">
-        <v>1</v>
-      </c>
-      <c r="G73" s="17">
+      <c r="F74" s="7">
+        <v>1</v>
+      </c>
+      <c r="G74" s="17">
         <v>43986</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F74" s="4">
-        <v>1</v>
-      </c>
-      <c r="G74" s="17">
-        <v>43984</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="9" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>189</v>
+        <v>27</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F75" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="G75" s="19">
-        <v>43983</v>
+        <v>1</v>
+      </c>
+      <c r="G75" s="18">
+        <v>43984</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B76" s="46" t="s">
+        <v>187</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F76" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G76" s="18">
+        <v>43983</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E77" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="B76" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D76" s="9" t="s">
+      <c r="F77" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="G77" s="18">
+        <v>43983</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="B78" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="F76" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="G76" s="19">
-        <v>43983</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="48" t="s">
+      <c r="C78" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D78" s="5" t="s">
         <v>196</v>
-      </c>
-      <c r="B77" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="C77" s="50" t="s">
-        <v>105</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="E77" s="10" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D77)</f>
-        <v>https://www.coursera.org/verify/ZM9BMYXLN942</v>
-      </c>
-      <c r="F77" s="13">
-        <v>0.83</v>
-      </c>
-      <c r="G77" s="19">
-        <v>43983</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="E78" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D78)</f>
-        <v>https://www.coursera.org/verify/FKLHXG2L7ZV2</v>
-      </c>
-      <c r="F78" s="4">
-        <v>1</v>
+        <v>https://www.coursera.org/verify/ZM9BMYXLN942</v>
+      </c>
+      <c r="F78" s="7">
+        <v>0.83</v>
       </c>
       <c r="G78" s="17">
-        <v>43978</v>
+        <v>43983</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E79" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D79)</f>
-        <v>https://www.coursera.org/verify/LSGX9WZD2829</v>
+        <v>https://www.coursera.org/verify/FKLHXG2L7ZV2</v>
       </c>
       <c r="F79" s="4">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G79" s="17">
-        <v>43968</v>
+        <v>43978</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="9" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>28</v>
+        <v>102</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>205</v>
+        <v>200</v>
+      </c>
+      <c r="E80" s="10" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D80)</f>
+        <v>https://www.coursera.org/verify/LSGX9WZD2829</v>
       </c>
       <c r="F80" s="11">
-        <v>1</v>
-      </c>
-      <c r="G80" s="19">
-        <v>43965</v>
+        <v>0.98</v>
+      </c>
+      <c r="G80" s="18">
+        <v>43968</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>207</v>
+        <v>27</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="F81" s="4">
         <v>1</v>
       </c>
       <c r="G81" s="17">
-        <v>43956</v>
+        <v>43965</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="9" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>212</v>
+        <v>108</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="F82" s="11">
         <v>1</v>
       </c>
-      <c r="G82" s="19">
-        <v>43953</v>
+      <c r="G82" s="18">
+        <v>43956</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="9" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>28</v>
+        <v>209</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F83" s="11">
         <v>1</v>
       </c>
-      <c r="G83" s="19">
-        <v>43871</v>
+      <c r="G83" s="18">
+        <v>43953</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F84" s="11">
+        <v>1</v>
+      </c>
+      <c r="G84" s="18">
+        <v>43871</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E85" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D84" s="9" t="s">
+      <c r="F85" s="11">
+        <v>1</v>
+      </c>
+      <c r="G85" s="18">
+        <v>43551</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="B86" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="F84" s="11">
-        <v>1</v>
-      </c>
-      <c r="G84" s="19">
-        <v>43551</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="2" t="s">
+      <c r="C86" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="D86" s="57" t="s">
         <v>221</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="E86" s="60" t="s">
         <v>222</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F85" s="4">
-        <v>1</v>
-      </c>
-      <c r="G85" s="17">
+      <c r="F86" s="61">
+        <v>1</v>
+      </c>
+      <c r="G86" s="63">
         <v>43549</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G85" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G85">
-      <sortCondition descending="1" ref="G1:G85"/>
+  <autoFilter ref="A1:G86" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G86">
+      <sortCondition descending="1" ref="G1:G86"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="E85" r:id="rId1" xr:uid="{6C0DBD8A-06FB-4276-97CC-44F7D2A620D3}"/>
-    <hyperlink ref="E84" r:id="rId2" xr:uid="{A3AA2B4E-A070-4264-BAD0-50B1BD9F111B}"/>
-    <hyperlink ref="E83" r:id="rId3" xr:uid="{9B48E280-22D3-4A9E-8D60-7F69F560315A}"/>
-    <hyperlink ref="E81" r:id="rId4" xr:uid="{A1888FFC-F836-43B1-ACCE-D7ED9F0B270F}"/>
-    <hyperlink ref="E82" r:id="rId5" xr:uid="{1D430177-A56E-4567-8FAC-5E8420D918CC}"/>
-    <hyperlink ref="E79" r:id="rId6" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{1F5AE59F-A263-4228-9C7E-266BAD69AD6D}"/>
-    <hyperlink ref="E80" r:id="rId7" xr:uid="{CE2198E5-2DEE-4B00-8F0C-17EA31FD42CF}"/>
-    <hyperlink ref="E74" r:id="rId8" xr:uid="{D9C0C981-CB38-4235-A77B-7B73A8D1355B}"/>
-    <hyperlink ref="E75" r:id="rId9" xr:uid="{256B4442-C33A-484D-A51A-03B0A68C0D1A}"/>
-    <hyperlink ref="E76" r:id="rId10" xr:uid="{11511F3E-24A6-40DC-8710-D6F763ABC7D0}"/>
-    <hyperlink ref="E68" r:id="rId11" display="https://www.hackerrank.com/certificates/2766975846a6" xr:uid="{23538072-30C4-4325-A871-9979C940114B}"/>
-    <hyperlink ref="E69" r:id="rId12" display="https://www.hackerrank.com/certificates/1140c95b9b14" xr:uid="{92658253-7FDE-4177-9BB5-57ABBEC11707}"/>
-    <hyperlink ref="E67" r:id="rId13" display="https://www.hackerrank.com/certificates/867daffabda4" xr:uid="{760F6237-ED74-4C76-921F-A92DB49AA851}"/>
-    <hyperlink ref="E40" r:id="rId14" xr:uid="{BE109821-CCDD-4A04-981A-9F6EFC5839F3}"/>
-    <hyperlink ref="E38" r:id="rId15" display="https://www.hackerrank.com/certificates/3af4ddb28fab" xr:uid="{193C03FB-8BC6-4219-AB14-ECE3411E93FC}"/>
-    <hyperlink ref="E35" r:id="rId16" xr:uid="{C4C48324-FD2D-4D60-97F7-1C543194CDA1}"/>
-    <hyperlink ref="E34" r:id="rId17" xr:uid="{24CD5469-5A68-4595-8905-E3195BAA26D6}"/>
-    <hyperlink ref="E33" r:id="rId18" display="https://www.hackerrank.com/certificates/6730cf1d0f21" xr:uid="{4E5A9F5D-377D-4813-82DA-653909A03F55}"/>
-    <hyperlink ref="E32" r:id="rId19" xr:uid="{13330E2D-247C-4D68-B3A4-25AEC2481299}"/>
-    <hyperlink ref="E13" r:id="rId20" xr:uid="{104CE576-4E8E-4A67-852D-469446BC152A}"/>
-    <hyperlink ref="E10" r:id="rId21" xr:uid="{F5B1676B-40C2-41E4-8A7C-EE0DDF96B5AB}"/>
-    <hyperlink ref="E11" r:id="rId22" xr:uid="{CF1353C0-1B68-45EB-B9D3-B3815B4819F9}"/>
-    <hyperlink ref="E12" r:id="rId23" xr:uid="{C08302DF-FF6D-47C0-8C56-3AB13A011040}"/>
-    <hyperlink ref="E14" r:id="rId24" display="https://olympus1.greatlearning.in/course_certificate/UAEGKOSB" xr:uid="{D327F964-4247-480C-ABF2-CE1C58A5C248}"/>
-    <hyperlink ref="E18" r:id="rId25" xr:uid="{899ABF8F-A4FE-4A5E-81D4-FDAA431DAB0E}"/>
-    <hyperlink ref="E23" r:id="rId26" display="https://www.hackerrank.com/certificates/cf58231a440f" xr:uid="{DE2CBB3E-53B4-4A72-B17A-95F8DC50A680}"/>
-    <hyperlink ref="E26" r:id="rId27" display="https://verify.greatlearning.in/SSMRYOWJ" xr:uid="{5873F399-7F29-4029-A2AF-C59477D7EEFA}"/>
-    <hyperlink ref="E27" r:id="rId28" display="https://verify.greatlearning.in/ZYQTXTJA" xr:uid="{9CE1A66B-C3BE-475F-9AAC-35D820A2B426}"/>
-    <hyperlink ref="E28" r:id="rId29" display="https://verify.greatlearning.in/GQGRZFQQ" xr:uid="{5442A54E-DEC1-418C-88C0-D3881C3E7DF7}"/>
-    <hyperlink ref="E24" r:id="rId30" display="https://www.hackerrank.com/certificates/4490b4a0e606" xr:uid="{03797E5A-D7A7-48A4-A1B4-62A5C7C463AF}"/>
-    <hyperlink ref="E25" r:id="rId31" display="https://www.hackerrank.com/certificates/fdeeaad81310" xr:uid="{0492AAD8-A54A-4838-943A-8F8C8C981536}"/>
-    <hyperlink ref="E30" r:id="rId32" display="https://www.hackerrank.com/certificates/1cadc360a79d" xr:uid="{D163DA80-AE56-4D17-80D1-BCE62B9B0E77}"/>
-    <hyperlink ref="E36" r:id="rId33" xr:uid="{7EB46669-C518-425D-8A3E-395F05BE96F4}"/>
-    <hyperlink ref="E56" r:id="rId34" xr:uid="{E604A0FD-1B8B-4069-A5D9-749A14F9519E}"/>
-    <hyperlink ref="E57" r:id="rId35" xr:uid="{6D72DCB3-71D9-4096-B636-A24037DEC0A0}"/>
-    <hyperlink ref="E58" r:id="rId36" xr:uid="{F48B074D-BE93-4758-BDD0-50BF937B211E}"/>
-    <hyperlink ref="E9" r:id="rId37" xr:uid="{7F8992C5-905E-4B72-82BE-676D324D1D17}"/>
-    <hyperlink ref="E78" r:id="rId38" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{C875791B-2744-4F5C-9948-8B038AB7B795}"/>
+    <hyperlink ref="E86" r:id="rId1" xr:uid="{6C0DBD8A-06FB-4276-97CC-44F7D2A620D3}"/>
+    <hyperlink ref="E85" r:id="rId2" xr:uid="{A3AA2B4E-A070-4264-BAD0-50B1BD9F111B}"/>
+    <hyperlink ref="E84" r:id="rId3" xr:uid="{9B48E280-22D3-4A9E-8D60-7F69F560315A}"/>
+    <hyperlink ref="E82" r:id="rId4" xr:uid="{A1888FFC-F836-43B1-ACCE-D7ED9F0B270F}"/>
+    <hyperlink ref="E83" r:id="rId5" xr:uid="{1D430177-A56E-4567-8FAC-5E8420D918CC}"/>
+    <hyperlink ref="E80" r:id="rId6" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{1F5AE59F-A263-4228-9C7E-266BAD69AD6D}"/>
+    <hyperlink ref="E81" r:id="rId7" xr:uid="{CE2198E5-2DEE-4B00-8F0C-17EA31FD42CF}"/>
+    <hyperlink ref="E75" r:id="rId8" xr:uid="{D9C0C981-CB38-4235-A77B-7B73A8D1355B}"/>
+    <hyperlink ref="E76" r:id="rId9" xr:uid="{256B4442-C33A-484D-A51A-03B0A68C0D1A}"/>
+    <hyperlink ref="E77" r:id="rId10" xr:uid="{11511F3E-24A6-40DC-8710-D6F763ABC7D0}"/>
+    <hyperlink ref="E69" r:id="rId11" display="https://www.hackerrank.com/certificates/2766975846a6" xr:uid="{23538072-30C4-4325-A871-9979C940114B}"/>
+    <hyperlink ref="E70" r:id="rId12" display="https://www.hackerrank.com/certificates/1140c95b9b14" xr:uid="{92658253-7FDE-4177-9BB5-57ABBEC11707}"/>
+    <hyperlink ref="E68" r:id="rId13" display="https://www.hackerrank.com/certificates/867daffabda4" xr:uid="{760F6237-ED74-4C76-921F-A92DB49AA851}"/>
+    <hyperlink ref="E41" r:id="rId14" xr:uid="{BE109821-CCDD-4A04-981A-9F6EFC5839F3}"/>
+    <hyperlink ref="E39" r:id="rId15" display="https://www.hackerrank.com/certificates/3af4ddb28fab" xr:uid="{193C03FB-8BC6-4219-AB14-ECE3411E93FC}"/>
+    <hyperlink ref="E36" r:id="rId16" xr:uid="{C4C48324-FD2D-4D60-97F7-1C543194CDA1}"/>
+    <hyperlink ref="E35" r:id="rId17" xr:uid="{24CD5469-5A68-4595-8905-E3195BAA26D6}"/>
+    <hyperlink ref="E34" r:id="rId18" display="https://www.hackerrank.com/certificates/6730cf1d0f21" xr:uid="{4E5A9F5D-377D-4813-82DA-653909A03F55}"/>
+    <hyperlink ref="E33" r:id="rId19" xr:uid="{13330E2D-247C-4D68-B3A4-25AEC2481299}"/>
+    <hyperlink ref="E14" r:id="rId20" xr:uid="{104CE576-4E8E-4A67-852D-469446BC152A}"/>
+    <hyperlink ref="E11" r:id="rId21" xr:uid="{F5B1676B-40C2-41E4-8A7C-EE0DDF96B5AB}"/>
+    <hyperlink ref="E12" r:id="rId22" xr:uid="{CF1353C0-1B68-45EB-B9D3-B3815B4819F9}"/>
+    <hyperlink ref="E13" r:id="rId23" xr:uid="{C08302DF-FF6D-47C0-8C56-3AB13A011040}"/>
+    <hyperlink ref="E15" r:id="rId24" display="https://olympus1.greatlearning.in/course_certificate/UAEGKOSB" xr:uid="{D327F964-4247-480C-ABF2-CE1C58A5C248}"/>
+    <hyperlink ref="E19" r:id="rId25" xr:uid="{899ABF8F-A4FE-4A5E-81D4-FDAA431DAB0E}"/>
+    <hyperlink ref="E24" r:id="rId26" display="https://www.hackerrank.com/certificates/cf58231a440f" xr:uid="{DE2CBB3E-53B4-4A72-B17A-95F8DC50A680}"/>
+    <hyperlink ref="E27" r:id="rId27" display="https://verify.greatlearning.in/SSMRYOWJ" xr:uid="{5873F399-7F29-4029-A2AF-C59477D7EEFA}"/>
+    <hyperlink ref="E28" r:id="rId28" display="https://verify.greatlearning.in/ZYQTXTJA" xr:uid="{9CE1A66B-C3BE-475F-9AAC-35D820A2B426}"/>
+    <hyperlink ref="E29" r:id="rId29" display="https://verify.greatlearning.in/GQGRZFQQ" xr:uid="{5442A54E-DEC1-418C-88C0-D3881C3E7DF7}"/>
+    <hyperlink ref="E25" r:id="rId30" display="https://www.hackerrank.com/certificates/4490b4a0e606" xr:uid="{03797E5A-D7A7-48A4-A1B4-62A5C7C463AF}"/>
+    <hyperlink ref="E26" r:id="rId31" display="https://www.hackerrank.com/certificates/fdeeaad81310" xr:uid="{0492AAD8-A54A-4838-943A-8F8C8C981536}"/>
+    <hyperlink ref="E31" r:id="rId32" display="https://www.hackerrank.com/certificates/1cadc360a79d" xr:uid="{D163DA80-AE56-4D17-80D1-BCE62B9B0E77}"/>
+    <hyperlink ref="E37" r:id="rId33" xr:uid="{7EB46669-C518-425D-8A3E-395F05BE96F4}"/>
+    <hyperlink ref="E57" r:id="rId34" xr:uid="{E604A0FD-1B8B-4069-A5D9-749A14F9519E}"/>
+    <hyperlink ref="E58" r:id="rId35" xr:uid="{6D72DCB3-71D9-4096-B636-A24037DEC0A0}"/>
+    <hyperlink ref="E59" r:id="rId36" xr:uid="{F48B074D-BE93-4758-BDD0-50BF937B211E}"/>
+    <hyperlink ref="E10" r:id="rId37" xr:uid="{7F8992C5-905E-4B72-82BE-676D324D1D17}"/>
+    <hyperlink ref="E79" r:id="rId38" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{C875791B-2744-4F5C-9948-8B038AB7B795}"/>
     <hyperlink ref="E29:E42" r:id="rId39" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{CE0B26B0-E940-4BD5-8F74-8D28A4F3B13A}"/>
-    <hyperlink ref="E37" r:id="rId40" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{5152B189-9CFA-4B7A-842F-93D4B5F53177}"/>
-    <hyperlink ref="E55" r:id="rId41" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{5C171493-E45D-436D-968B-6A7D6CED71CA}"/>
-    <hyperlink ref="E15" r:id="rId42" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{CC465E8A-1F75-432D-9DC6-368FD314B682}"/>
+    <hyperlink ref="E38" r:id="rId40" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{5152B189-9CFA-4B7A-842F-93D4B5F53177}"/>
+    <hyperlink ref="E56" r:id="rId41" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{5C171493-E45D-436D-968B-6A7D6CED71CA}"/>
+    <hyperlink ref="E16" r:id="rId42" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{CC465E8A-1F75-432D-9DC6-368FD314B682}"/>
     <hyperlink ref="E9:E10" r:id="rId43" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{C55AB7BE-0BE1-4CE1-8CFE-C0E7B2B0BA28}"/>
     <hyperlink ref="E12:E15" r:id="rId44" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{549C4CBA-43AF-4870-BE36-8D1CBC3CFD71}"/>
-    <hyperlink ref="E31" r:id="rId45" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{53B8A539-1C54-4D29-828E-465373C8A2C4}"/>
-    <hyperlink ref="E63" r:id="rId46" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{6D2FD0D9-7715-4D27-986B-9CBDCC24BC65}"/>
-    <hyperlink ref="E8" r:id="rId47" xr:uid="{699CE3D0-7418-4EFB-9798-81677CCAC0DE}"/>
-    <hyperlink ref="E7" r:id="rId48" display="https://www.hackerrank.com/certificates/eafe133d26dc" xr:uid="{3748E750-A80A-4402-BC5F-803B16F27441}"/>
-    <hyperlink ref="E4" r:id="rId49" xr:uid="{59D89928-3553-4495-8CD7-92EBC3B422E3}"/>
-    <hyperlink ref="E3" r:id="rId50" xr:uid="{90A10946-4B5C-4200-83CE-B2047CBD914F}"/>
-    <hyperlink ref="E2" r:id="rId51" xr:uid="{3280A986-162F-4133-9109-1EE526FB0D39}"/>
+    <hyperlink ref="E32" r:id="rId45" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{53B8A539-1C54-4D29-828E-465373C8A2C4}"/>
+    <hyperlink ref="E64" r:id="rId46" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{6D2FD0D9-7715-4D27-986B-9CBDCC24BC65}"/>
+    <hyperlink ref="E9" r:id="rId47" xr:uid="{699CE3D0-7418-4EFB-9798-81677CCAC0DE}"/>
+    <hyperlink ref="E8" r:id="rId48" display="https://www.hackerrank.com/certificates/eafe133d26dc" xr:uid="{3748E750-A80A-4402-BC5F-803B16F27441}"/>
+    <hyperlink ref="E5" r:id="rId49" xr:uid="{59D89928-3553-4495-8CD7-92EBC3B422E3}"/>
+    <hyperlink ref="E4" r:id="rId50" xr:uid="{90A10946-4B5C-4200-83CE-B2047CBD914F}"/>
+    <hyperlink ref="E3" r:id="rId51" xr:uid="{3280A986-162F-4133-9109-1EE526FB0D39}"/>
+    <hyperlink ref="E2" r:id="rId52" xr:uid="{0A52842B-3BD1-4EDE-ABBA-FF846F26BE9D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3682,34 +3746,34 @@
     <col min="3" max="3" width="112.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="22.44140625" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.44140625" style="21" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.44140625" customWidth="1"/>
     <col min="9" max="9" width="107.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>224</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="D1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="E1" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="G1" s="25" t="s">
         <v>229</v>
       </c>
-      <c r="F1" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="23" t="s">
         <v>3</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -3718,226 +3782,226 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>323</v>
-      </c>
-      <c r="C2" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="D2" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>320</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F2" s="26">
+        <v>44652</v>
+      </c>
+      <c r="G2" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="F2" s="27">
-        <v>44652</v>
-      </c>
-      <c r="G2" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>232</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="24" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="D3" s="25" t="s">
+      <c r="E3" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F3" s="26">
+        <v>44470</v>
+      </c>
+      <c r="G3" s="26">
+        <v>44651</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F3" s="27">
-        <v>44470</v>
-      </c>
-      <c r="G3" s="27">
-        <v>44651</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>237</v>
       </c>
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="E4" s="24" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="F4" s="19">
+        <v>44378</v>
+      </c>
+      <c r="G4" s="19">
+        <v>44469</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="I4" s="5"/>
+    </row>
+    <row r="5" spans="1:9" s="32" customFormat="1">
+      <c r="A5" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="C5" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F5" s="19">
+        <v>44263</v>
+      </c>
+      <c r="G5" s="19">
+        <v>44377</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="E4" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="20">
-        <v>44378</v>
-      </c>
-      <c r="G4" s="20">
-        <v>44469</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" s="33" customFormat="1">
-      <c r="A5" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="I5" s="5"/>
+    </row>
+    <row r="6" spans="1:9" ht="57.6">
+      <c r="A6" s="27" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="B6" s="27" t="s">
         <v>242</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="C6" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="F6" s="30">
+        <v>44137</v>
+      </c>
+      <c r="G6" s="30">
+        <v>44200</v>
+      </c>
+      <c r="H6" s="27" t="s">
         <v>235</v>
       </c>
-      <c r="E5" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F5" s="20">
-        <v>44263</v>
-      </c>
-      <c r="G5" s="20">
-        <v>44377</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="57.6">
-      <c r="A6" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" s="28" t="s">
+      <c r="I6" s="31" t="s">
         <v>244</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>245</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>240</v>
-      </c>
-      <c r="F6" s="31">
-        <v>44137</v>
-      </c>
-      <c r="G6" s="31">
-        <v>44200</v>
-      </c>
-      <c r="H6" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D7" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F7" s="19">
+        <v>44136</v>
+      </c>
+      <c r="G7" s="19">
+        <v>44166</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>249</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="E7" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F7" s="20">
-        <v>44136</v>
-      </c>
-      <c r="G7" s="20">
-        <v>44166</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F8" s="19">
+        <v>44105</v>
+      </c>
+      <c r="G8" s="19">
+        <v>44136</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="E8" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F8" s="20">
-        <v>44105</v>
-      </c>
-      <c r="G8" s="20">
-        <v>44136</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="I8" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D9" s="24" t="s">
         <v>254</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="E9" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="F9" s="26">
+        <v>43432</v>
+      </c>
+      <c r="G9" s="26">
+        <v>43442</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>255</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="E9" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F9" s="27">
-        <v>43432</v>
-      </c>
-      <c r="G9" s="27">
-        <v>43442</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3946,8 +4010,8 @@
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
@@ -3957,8 +4021,8 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
@@ -3968,8 +4032,8 @@
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
@@ -3991,7 +4055,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718451B2-E12D-4ABD-B26C-5975AED3964E}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -3999,16 +4063,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="37" t="s">
-        <v>258</v>
-      </c>
-      <c r="B1" s="37" t="s">
-        <v>259</v>
+      <c r="A1" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B2" s="7">
         <v>0.9</v>
@@ -4019,12 +4083,12 @@
         <v>261</v>
       </c>
       <c r="B3" s="7">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B4" s="7">
         <v>0.8</v>
@@ -4032,7 +4096,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="B5" s="7">
         <v>0.8</v>
@@ -4040,15 +4104,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>263</v>
+        <v>213</v>
       </c>
       <c r="B6" s="7">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>264</v>
+        <v>327</v>
       </c>
       <c r="B7" s="7">
         <v>0.8</v>
@@ -4056,7 +4120,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B8" s="7">
         <v>0.8</v>
@@ -4064,7 +4128,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B9" s="7">
         <v>0.8</v>
@@ -4072,39 +4136,39 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B10" s="7">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B11" s="7">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B12" s="7">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B13" s="7">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B14" s="7">
         <v>0.6</v>
@@ -4112,15 +4176,15 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B15" s="7">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B16" s="7">
         <v>0.6</v>
@@ -4128,7 +4192,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B17" s="7">
         <v>0.6</v>
@@ -4136,7 +4200,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B18" s="7">
         <v>0.6</v>
@@ -4144,7 +4208,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B19" s="7">
         <v>0.6</v>
@@ -4152,15 +4216,15 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B20" s="7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B21" s="7">
         <v>0.5</v>
@@ -4168,24 +4232,16 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B22" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B23" s="7">
-        <v>0.7</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:B22" xr:uid="{718451B2-E12D-4ABD-B26C-5975AED3964E}">
+  <autoFilter ref="A1:B21" xr:uid="{718451B2-E12D-4ABD-B26C-5975AED3964E}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B22">
-      <sortCondition descending="1" ref="B1:B22"/>
+      <sortCondition descending="1" ref="B1:B21"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4204,199 +4260,199 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="C1" s="38" t="s">
-        <v>281</v>
-      </c>
-      <c r="D1" s="38" t="s">
-        <v>282</v>
+      <c r="B1" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>288</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -4420,9 +4476,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4643,19 +4702,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F92213D-1611-4A06-8F7F-2A2F3FD54BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E4A532-34F4-4909-9773-2D1B4D74CA0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4680,9 +4735,10 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E4A532-34F4-4909-9773-2D1B4D74CA0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F92213D-1611-4A06-8F7F-2A2F3FD54BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/portfolios.xlsx
+++ b/portfolios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\jjnanthakumar.github.io\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Internal\Personal\jjnanthakumar.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A02A9A82-1BD7-4B96-8DF8-F59B30D051EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D091F0BB-D0A6-4910-ABE4-13C4FBD12C0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Certifications" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Projects" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Certifications!$A$1:$G$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Certifications!$A$1:$G$90</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Experience!$A$1:$I$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Skills!$A$1:$B$21</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="345">
   <si>
     <t>Title</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Microsoft</t>
   </si>
   <si>
-    <t>https://www.credly.com/badges/de23617e-5bbf-4da8-bd33-9025ba84933a/public_url</t>
-  </si>
-  <si>
     <t>AI ML WORKATHON 2021—Participant</t>
   </si>
   <si>
@@ -83,12 +80,6 @@
     <t>Microsoft Certified: Azure AI Fundamentals</t>
   </si>
   <si>
-    <t>I045-9367</t>
-  </si>
-  <si>
-    <t>https://www.credly.com/badges/bee3fafd-9644-4783-b3b0-3b96c0373e4c</t>
-  </si>
-  <si>
     <t>JavaScript (Intermediate)</t>
   </si>
   <si>
@@ -113,12 +104,6 @@
     <t>Microsoft Certified: Azure Data Fundamentals</t>
   </si>
   <si>
-    <t>H918-4797</t>
-  </si>
-  <si>
-    <t>https://www.credly.com/badges/aa538cc2-e9ed-4416-93be-b2daee06f072</t>
-  </si>
-  <si>
     <t>Intermediate Python</t>
   </si>
   <si>
@@ -152,9 +137,6 @@
     <t>Microsoft Certified: Azure Fundamentals</t>
   </si>
   <si>
-    <t>H953-9167</t>
-  </si>
-  <si>
     <t>Python for Beginners</t>
   </si>
   <si>
@@ -737,9 +719,6 @@
     <t>Junior Software Engineer</t>
   </si>
   <si>
-    <t>Currently Working on Azure DevOps and Azure Synapse Solution.</t>
-  </si>
-  <si>
     <t>Remote</t>
   </si>
   <si>
@@ -824,9 +803,6 @@
     <t>DJANGO</t>
   </si>
   <si>
-    <t>JAVA SCRIPT</t>
-  </si>
-  <si>
     <t>TKINTER</t>
   </si>
   <si>
@@ -866,9 +842,6 @@
     <t>POWER APPS</t>
   </si>
   <si>
-    <t>POWER AUTOMATE</t>
-  </si>
-  <si>
     <t>AZURE</t>
   </si>
   <si>
@@ -1001,28 +974,106 @@
     <t>Software Engineer</t>
   </si>
   <si>
-    <t>Currently Working on Azure Migration, Azure Synapse Solution and Django Web Application.</t>
-  </si>
-  <si>
-    <t>I340-8441</t>
-  </si>
-  <si>
     <t>Microsoft Certified: DevOps Engineer Expert</t>
   </si>
   <si>
-    <t>I365-1183</t>
-  </si>
-  <si>
-    <t>https://www.credly.com/badges/20ccf763-1844-43c2-a3bf-8571422339e1?source=jjnanthakumar.github.io</t>
-  </si>
-  <si>
-    <t>https://www.credly.com/badges/5b471ed6-57b5-466c-9d5c-654d5f5debca?jjnanthakumar.github.io</t>
-  </si>
-  <si>
     <t>July 22, 2022</t>
   </si>
   <si>
     <t>SQL</t>
+  </si>
+  <si>
+    <t>Currently Working on Full Stack Product development and Azure/Microsoft Fabric related activities.</t>
+  </si>
+  <si>
+    <t>Worked on Azure DevOps and Azure Synapse Solution.</t>
+  </si>
+  <si>
+    <t>Microsoft Certified: Azure Cosmos DB Developer Specialty</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/api/credentials/share/en-us/jjnanthakumar/AC13786EBE35AD82?sharingId=5F57043BDCEF700C</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/api/credentials/share/en-us/jjnanthakumar/39365FA45F8CB548?sharingId=5F57043BDCEF700C</t>
+  </si>
+  <si>
+    <t>September 20, 2024</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/api/credentials/share/en-us/jjnanthakumar/2D077E5A5CC7E496?sharingId=5F57043BDCEF700C</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/api/credentials/share/en-us/jjnanthakumar/2DCD504340C010CD?sharingId=5F57043BDCEF700C</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/api/credentials/share/en-us/jjnanthakumar/494A1AC865EEDE1C?sharingId=5F57043BDCEF700C</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/api/credentials/share/en-us/jjnanthakumar/486F9AEC4CC53623?sharingId=5F57043BDCEF700C</t>
+  </si>
+  <si>
+    <t>4OE2F5-C98DE0</t>
+  </si>
+  <si>
+    <t>B2S174-DD0105</t>
+  </si>
+  <si>
+    <t>445C4C-EV7FF8</t>
+  </si>
+  <si>
+    <t>F0HB13-142DBF</t>
+  </si>
+  <si>
+    <t>CC09C7-194ADE</t>
+  </si>
+  <si>
+    <t>F534V4-FF1CAC</t>
+  </si>
+  <si>
+    <t>https://www.hackerrank.com/certificates/fc61bc4aba8b</t>
+  </si>
+  <si>
+    <t>fc61bc4aba8b</t>
+  </si>
+  <si>
+    <t>Frontend Developer (React)</t>
+  </si>
+  <si>
+    <t>HackerRank (Role-based)</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/api/credentials/share/en-us/jjnanthakumar/61ABFFC661BD56AC?sharingId=5F57043BDCEF700C</t>
+  </si>
+  <si>
+    <t>61ABFFC661BD56AC</t>
+  </si>
+  <si>
+    <t>Implement security through a pipeline using Azure DevOps</t>
+  </si>
+  <si>
+    <t>Microsoft Applied Skills</t>
+  </si>
+  <si>
+    <t>January 13, 2024</t>
+  </si>
+  <si>
+    <t>January 7, 2024</t>
+  </si>
+  <si>
+    <t>4612B6E88897CAFC</t>
+  </si>
+  <si>
+    <t>Secure storage for Azure Files and Azure Blob Storage</t>
+  </si>
+  <si>
+    <t>October 28, 2023</t>
+  </si>
+  <si>
+    <t>https://learn.microsoft.com/api/credentials/share/en-us/jjnanthakumar/4612B6E88897CAFC?sharingId=5F57043BDCEF700C</t>
+  </si>
+  <si>
+    <t>JAVASCRIPT</t>
   </si>
 </sst>
 </file>
@@ -1217,7 +1268,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1298,7 +1349,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1625,16 +1675,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="65.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="44.44140625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="102" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.109375" style="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="55.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="105.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" style="21" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1661,8 +1711,8 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="54" t="s">
-        <v>322</v>
+      <c r="A2" s="50" t="s">
+        <v>316</v>
       </c>
       <c r="B2" s="50" t="s">
         <v>8</v>
@@ -1670,45 +1720,45 @@
       <c r="C2" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="54" t="s">
-        <v>323</v>
-      </c>
-      <c r="E2" s="55" t="s">
-        <v>324</v>
+      <c r="D2" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="54" t="s">
+        <v>318</v>
       </c>
       <c r="F2" s="52">
-        <v>0.92</v>
-      </c>
-      <c r="G2" s="56" t="s">
-        <v>326</v>
+        <v>0.9</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="50" t="s">
-        <v>7</v>
+        <v>341</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>8</v>
+        <v>337</v>
       </c>
       <c r="C3" s="50" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="E3" s="51" t="s">
-        <v>9</v>
+        <v>340</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>343</v>
       </c>
       <c r="F3" s="52">
-        <v>0.85</v>
-      </c>
-      <c r="G3" s="53">
-        <v>44560</v>
+        <v>1</v>
+      </c>
+      <c r="G3" s="55" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="50" t="s">
-        <v>10</v>
+        <v>311</v>
       </c>
       <c r="B4" s="50" t="s">
         <v>8</v>
@@ -1717,116 +1767,113 @@
         <v>8</v>
       </c>
       <c r="D4" s="50" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="51" t="s">
-        <v>12</v>
+        <v>324</v>
+      </c>
+      <c r="E4" s="54" t="s">
+        <v>317</v>
       </c>
       <c r="F4" s="52">
-        <v>1</v>
-      </c>
-      <c r="G4" s="53">
-        <v>44552</v>
+        <v>0.92</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="38" t="s">
+      <c r="A5" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>331</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="F5" s="52">
+        <v>1</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="D6" s="50" t="s">
+        <v>335</v>
+      </c>
+      <c r="E6" s="54" t="s">
+        <v>334</v>
+      </c>
+      <c r="F6" s="52">
+        <v>1</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="40">
-        <v>0.98</v>
-      </c>
-      <c r="G5" s="26">
-        <v>44527</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="33" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D6)</f>
-        <v>https://www.hackerrank.com/certificates/524e499db551</v>
-      </c>
-      <c r="F6" s="13">
-        <v>1</v>
-      </c>
-      <c r="G6" s="26">
-        <v>44493</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="33" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D7)</f>
-        <v>https://www.hackerrank.com/certificates/7a872682b210</v>
-      </c>
-      <c r="F7" s="13">
-        <v>1</v>
-      </c>
-      <c r="G7" s="39">
-        <v>44490</v>
+      <c r="C7" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>326</v>
+      </c>
+      <c r="E7" s="51" t="s">
+        <v>320</v>
+      </c>
+      <c r="F7" s="52">
+        <v>0.85</v>
+      </c>
+      <c r="G7" s="53">
+        <v>44560</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="50" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="57" t="s">
-        <v>17</v>
+        <v>9</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>8</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="51" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D8)</f>
-        <v>https://www.hackerrank.com/certificates/eafe133d26dc</v>
+        <v>10</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>11</v>
       </c>
       <c r="F8" s="52">
         <v>1</v>
       </c>
       <c r="G8" s="53">
-        <v>44469</v>
+        <v>44552</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="38" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B9" s="38" t="s">
         <v>8</v>
@@ -1835,1902 +1882,2000 @@
         <v>8</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>24</v>
+        <v>327</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>25</v>
+        <v>321</v>
       </c>
       <c r="F9" s="40">
-        <v>0.94</v>
+        <v>0.98</v>
       </c>
       <c r="G9" s="26">
-        <v>44439</v>
+        <v>44527</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>29</v>
+        <v>13</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="43" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="33" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D10)</f>
+        <v>https://www.hackerrank.com/certificates/524e499db551</v>
       </c>
       <c r="F10" s="13">
         <v>1</v>
       </c>
       <c r="G10" s="26">
-        <v>44419</v>
+        <v>44493</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>14</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>32</v>
+        <v>17</v>
+      </c>
+      <c r="E11" s="33" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D11)</f>
+        <v>https://www.hackerrank.com/certificates/7a872682b210</v>
       </c>
       <c r="F11" s="13">
         <v>1</v>
       </c>
       <c r="G11" s="39">
-        <v>44418</v>
+        <v>44490</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>27</v>
+        <v>18</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>14</v>
       </c>
       <c r="D12" s="50" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="51" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="E12" s="51" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D12)</f>
+        <v>https://www.hackerrank.com/certificates/eafe133d26dc</v>
       </c>
       <c r="F12" s="52">
         <v>1</v>
       </c>
       <c r="G12" s="53">
-        <v>44418</v>
+        <v>44469</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="24" t="s">
+      <c r="A13" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="F13" s="35">
-        <v>0.88</v>
+      <c r="D13" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="E13" s="45" t="s">
+        <v>322</v>
+      </c>
+      <c r="F13" s="40">
+        <v>0.94</v>
       </c>
       <c r="G13" s="26">
-        <v>44412</v>
+        <v>44439</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="7">
-        <v>1</v>
-      </c>
-      <c r="G14" s="19">
-        <v>44388</v>
+      <c r="A14" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="13">
+        <v>1</v>
+      </c>
+      <c r="G14" s="26">
+        <v>44419</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="12" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="E15" s="6" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D15)</f>
-        <v>https://verify.greatlearning.in/UAEGKOSB</v>
+        <v>26</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>27</v>
       </c>
       <c r="F15" s="13">
         <v>1</v>
       </c>
-      <c r="G15" s="20">
-        <v>44348</v>
+      <c r="G15" s="39">
+        <v>44418</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E16" s="33" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D16)</f>
-        <v>https://ude.my/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707</v>
-      </c>
-      <c r="F16" s="13">
-        <v>1</v>
-      </c>
-      <c r="G16" s="20">
-        <v>44346</v>
+      <c r="A16" s="50" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="52">
+        <v>1</v>
+      </c>
+      <c r="G16" s="53">
+        <v>44418</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="6" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D17)</f>
-        <v>https://ude.my/UC-a3ba46b5-170d-4510-a813-c3dff69a6697</v>
-      </c>
-      <c r="F17" s="7">
-        <v>1</v>
-      </c>
-      <c r="G17" s="19">
-        <v>44339</v>
+      <c r="A17" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>329</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="F17" s="35">
+        <v>0.88</v>
+      </c>
+      <c r="G17" s="26">
+        <v>44412</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="5" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="6" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D18)</f>
-        <v>https://ude.my/UC-6ee1aa7b-93ad-4437-ac78-fb96957a2f3b</v>
+        <v>33</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="F18" s="7">
         <v>1</v>
       </c>
       <c r="G18" s="19">
-        <v>44332</v>
+        <v>44388</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="7">
-        <v>1</v>
-      </c>
-      <c r="G19" s="19">
-        <v>44312</v>
+      <c r="A19" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="6" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D19)</f>
+        <v>https://verify.greatlearning.in/UAEGKOSB</v>
+      </c>
+      <c r="F19" s="13">
+        <v>1</v>
+      </c>
+      <c r="G19" s="20">
+        <v>44348</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="34" t="str">
+      <c r="A20" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="33" t="str">
         <f>HYPERLINK("https://ude.my/"&amp; D20)</f>
-        <v>https://ude.my/UC-c9ca1de5-ac7a-449c-923d-aa727cbd1906</v>
-      </c>
-      <c r="F20" s="35">
-        <v>1</v>
-      </c>
-      <c r="G20" s="26">
-        <v>44312</v>
+        <v>https://ude.my/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707</v>
+      </c>
+      <c r="F20" s="13">
+        <v>1</v>
+      </c>
+      <c r="G20" s="20">
+        <v>44346</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>62</v>
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="E21" s="6" t="str">
         <f>HYPERLINK("https://ude.my/"&amp; D21)</f>
-        <v>https://ude.my/UC-b2d528a0-beba-44fc-96bb-c1ccd88ee68a</v>
-      </c>
-      <c r="F21" s="13">
-        <v>1</v>
-      </c>
-      <c r="G21" s="20">
-        <v>44309</v>
+        <v>https://ude.my/UC-a3ba46b5-170d-4510-a813-c3dff69a6697</v>
+      </c>
+      <c r="F21" s="7">
+        <v>1</v>
+      </c>
+      <c r="G21" s="19">
+        <v>44339</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="A22" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E22" s="33" t="str">
+      <c r="C22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="6" t="str">
         <f>HYPERLINK("https://ude.my/"&amp; D22)</f>
-        <v>https://ude.my/UC-1f46a0d1-37f4-4a8c-95f6-839311438ab7</v>
-      </c>
-      <c r="F22" s="13">
-        <v>1</v>
-      </c>
-      <c r="G22" s="20">
-        <v>44306</v>
+        <v>https://ude.my/UC-6ee1aa7b-93ad-4437-ac78-fb96957a2f3b</v>
+      </c>
+      <c r="F22" s="7">
+        <v>1</v>
+      </c>
+      <c r="G22" s="19">
+        <v>44332</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="5" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="6" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D23)</f>
+        <v>50</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="7">
+        <v>1</v>
+      </c>
+      <c r="G23" s="19">
+        <v>44312</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="34" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D24)</f>
+        <v>https://ude.my/UC-c9ca1de5-ac7a-449c-923d-aa727cbd1906</v>
+      </c>
+      <c r="F24" s="35">
+        <v>1</v>
+      </c>
+      <c r="G24" s="26">
+        <v>44312</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="6" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D25)</f>
+        <v>https://ude.my/UC-b2d528a0-beba-44fc-96bb-c1ccd88ee68a</v>
+      </c>
+      <c r="F25" s="13">
+        <v>1</v>
+      </c>
+      <c r="G25" s="20">
+        <v>44309</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E26" s="33" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D26)</f>
+        <v>https://ude.my/UC-1f46a0d1-37f4-4a8c-95f6-839311438ab7</v>
+      </c>
+      <c r="F26" s="13">
+        <v>1</v>
+      </c>
+      <c r="G26" s="20">
+        <v>44306</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="6" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D27)</f>
         <v>https://ude.my/UC-18dd832f-d345-44f1-92cf-281f71e773d1</v>
       </c>
-      <c r="F23" s="7">
-        <v>1</v>
-      </c>
-      <c r="G23" s="19">
+      <c r="F27" s="7">
+        <v>1</v>
+      </c>
+      <c r="G27" s="19">
         <v>44300</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E24" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D24)</f>
-        <v>https://www.hackerrank.com/certificates/cf58231a440f</v>
-      </c>
-      <c r="F24" s="7">
-        <v>1</v>
-      </c>
-      <c r="G24" s="19">
-        <v>44288</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E25" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D25)</f>
-        <v>https://www.hackerrank.com/certificates/4490b4a0e606</v>
-      </c>
-      <c r="F25" s="7">
-        <v>1</v>
-      </c>
-      <c r="G25" s="19">
-        <v>44288</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>74</v>
-      </c>
-      <c r="E26" s="34" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D26)</f>
-        <v>https://www.hackerrank.com/certificates/fdeeaad81310</v>
-      </c>
-      <c r="F26" s="35">
-        <v>1</v>
-      </c>
-      <c r="G26" s="26">
-        <v>44288</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="34" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D27)</f>
-        <v>https://verify.greatlearning.in/SSMRYOWJ</v>
-      </c>
-      <c r="F27" s="40">
-        <v>1</v>
-      </c>
-      <c r="G27" s="39">
-        <v>44287</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="6" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D28)</f>
+        <v>https://www.hackerrank.com/certificates/cf58231a440f</v>
+      </c>
+      <c r="F28" s="7">
+        <v>1</v>
+      </c>
+      <c r="G28" s="19">
+        <v>44288</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" s="6" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D29)</f>
+        <v>https://www.hackerrank.com/certificates/4490b4a0e606</v>
+      </c>
+      <c r="F29" s="7">
+        <v>1</v>
+      </c>
+      <c r="G29" s="19">
+        <v>44288</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="34" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D30)</f>
+        <v>https://www.hackerrank.com/certificates/fdeeaad81310</v>
+      </c>
+      <c r="F30" s="35">
+        <v>1</v>
+      </c>
+      <c r="G30" s="26">
+        <v>44288</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E31" s="34" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D31)</f>
+        <v>https://verify.greatlearning.in/SSMRYOWJ</v>
+      </c>
+      <c r="F31" s="40">
+        <v>1</v>
+      </c>
+      <c r="G31" s="39">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="6" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D32)</f>
+        <v>https://verify.greatlearning.in/ZYQTXTJA</v>
+      </c>
+      <c r="F32" s="13">
+        <v>1</v>
+      </c>
+      <c r="G32" s="20">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="6" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D33)</f>
+        <v>https://verify.greatlearning.in/GQGRZFQQ</v>
+      </c>
+      <c r="F33" s="13">
+        <v>1</v>
+      </c>
+      <c r="G33" s="19">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="33" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D34)</f>
+        <v>https://verify.greatlearning.in/HSNELKCZ</v>
+      </c>
+      <c r="F34" s="13">
+        <v>1</v>
+      </c>
+      <c r="G34" s="20">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="B35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E28" s="6" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D28)</f>
-        <v>https://verify.greatlearning.in/ZYQTXTJA</v>
-      </c>
-      <c r="F28" s="13">
-        <v>1</v>
-      </c>
-      <c r="G28" s="20">
-        <v>44287</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="12" t="s">
+      <c r="E35" s="6" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D35)</f>
+        <v>https://www.hackerrank.com/certificates/1cadc360a79d</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1</v>
+      </c>
+      <c r="G35" s="19">
+        <v>44268</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D29" s="12" t="s">
+      <c r="B36" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="E29" s="6" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D29)</f>
-        <v>https://verify.greatlearning.in/GQGRZFQQ</v>
-      </c>
-      <c r="F29" s="13">
-        <v>1</v>
-      </c>
-      <c r="G29" s="19">
-        <v>44287</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="12" t="s">
+      <c r="C36" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="33" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D30)</f>
-        <v>https://verify.greatlearning.in/HSNELKCZ</v>
-      </c>
-      <c r="F30" s="13">
-        <v>1</v>
-      </c>
-      <c r="G30" s="20">
-        <v>44287</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D31)</f>
-        <v>https://www.hackerrank.com/certificates/1cadc360a79d</v>
-      </c>
-      <c r="F31" s="7">
-        <v>1</v>
-      </c>
-      <c r="G31" s="19">
-        <v>44268</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>87</v>
-      </c>
-      <c r="E32" s="34" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D32)</f>
+      <c r="E36" s="34" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D36)</f>
         <v>https://ude.my/UC-61e2521b-a9bb-48dc-bb44-3679ba047cf8</v>
       </c>
-      <c r="F32" s="35">
-        <v>1</v>
-      </c>
-      <c r="G32" s="26">
+      <c r="F36" s="35">
+        <v>1</v>
+      </c>
+      <c r="G36" s="26">
         <v>44249</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="F33" s="7">
-        <v>0.97</v>
-      </c>
-      <c r="G33" s="17">
-        <v>44246</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D34)</f>
-        <v>https://www.hackerrank.com/certificates/6730CF1D0F21</v>
-      </c>
-      <c r="F34" s="7">
-        <v>1</v>
-      </c>
-      <c r="G34" s="17">
-        <v>44209</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F35" s="13">
-        <v>1</v>
-      </c>
-      <c r="G35" s="18">
-        <v>44180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" s="8">
-        <v>271676</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F36" s="7">
-        <v>1</v>
-      </c>
-      <c r="G36" s="18">
-        <v>44176</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="5" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" s="8">
-        <v>271676</v>
+        <v>83</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="F37" s="7">
-        <v>1</v>
-      </c>
-      <c r="G37" s="20">
-        <v>44176</v>
+        <v>0.97</v>
+      </c>
+      <c r="G37" s="17">
+        <v>44246</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="5" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>103</v>
+        <v>14</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="E38" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D38)</f>
-        <v>https://www.coursera.org/verify/3NB72YUYKWLV</v>
+        <v>87</v>
+      </c>
+      <c r="E38" s="6" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D38)</f>
+        <v>https://www.hackerrank.com/certificates/6730CF1D0F21</v>
       </c>
       <c r="F38" s="7">
         <v>1</v>
       </c>
-      <c r="G38" s="18">
-        <v>44165</v>
+      <c r="G38" s="17">
+        <v>44209</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>17</v>
+      <c r="A39" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E39" s="6" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D39)</f>
-        <v>https://www.hackerrank.com/certificates/3AF4DDB28FAB</v>
-      </c>
-      <c r="F39" s="7">
+        <v>22</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F39" s="13">
         <v>1</v>
       </c>
       <c r="G39" s="18">
-        <v>44146</v>
+        <v>44180</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>108</v>
+        <v>91</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>92</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D40)</f>
-        <v>https://www.coursera.org/verify/AW6A4NWBVJ9V</v>
+        <v>93</v>
+      </c>
+      <c r="D40" s="8">
+        <v>271676</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="F40" s="7">
         <v>1</v>
       </c>
       <c r="G40" s="18">
-        <v>44135</v>
+        <v>44176</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>111</v>
+      <c r="A41" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>93</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D41" s="12" t="s">
-        <v>113</v>
+        <v>93</v>
+      </c>
+      <c r="D41" s="8">
+        <v>271676</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="F41" s="7">
         <v>1</v>
       </c>
-      <c r="G41" s="18">
-        <v>44135</v>
+      <c r="G41" s="20">
+        <v>44176</v>
       </c>
     </row>
     <row r="42" spans="1:7">
-      <c r="A42" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>102</v>
+      <c r="A42" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>116</v>
+        <v>97</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>98</v>
       </c>
       <c r="E42" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D42)</f>
-        <v>https://www.coursera.org/verify/3WQ6APAJLP9T</v>
-      </c>
-      <c r="F42" s="16">
+        <v>https://www.coursera.org/verify/3NB72YUYKWLV</v>
+      </c>
+      <c r="F42" s="7">
         <v>1</v>
       </c>
       <c r="G42" s="18">
-        <v>44126</v>
+        <v>44165</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="5" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>103</v>
+        <v>14</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D43)</f>
-        <v>https://www.coursera.org/verify/8DZVQYMNERJA</v>
-      </c>
-      <c r="F43" s="16">
+        <v>100</v>
+      </c>
+      <c r="E43" s="6" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D43)</f>
+        <v>https://www.hackerrank.com/certificates/3AF4DDB28FAB</v>
+      </c>
+      <c r="F43" s="7">
         <v>1</v>
       </c>
       <c r="G43" s="18">
-        <v>44126</v>
+        <v>44146</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="5" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="E44" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D44)</f>
-        <v>https://www.coursera.org/verify/specialization/LGGYURMTBUUG</v>
-      </c>
-      <c r="F44" s="16">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D44)</f>
+        <v>https://www.coursera.org/verify/AW6A4NWBVJ9V</v>
+      </c>
+      <c r="F44" s="7">
         <v>1</v>
       </c>
       <c r="G44" s="18">
+        <v>44135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F45" s="7">
+        <v>1</v>
+      </c>
+      <c r="G45" s="18">
+        <v>44135</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E46" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D46)</f>
+        <v>https://www.coursera.org/verify/3WQ6APAJLP9T</v>
+      </c>
+      <c r="F46" s="16">
+        <v>1</v>
+      </c>
+      <c r="G46" s="18">
         <v>44126</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E45" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D45)</f>
-        <v>https://www.coursera.org/verify/LVBJNAL79BLV</v>
-      </c>
-      <c r="F45" s="16">
-        <v>0.97</v>
-      </c>
-      <c r="G45" s="18">
-        <v>44124</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E46" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D46)</f>
-        <v>https://www.coursera.org/verify/specialization/6NXPUFTEK3Z7</v>
-      </c>
-      <c r="F46" s="16">
-        <v>1</v>
-      </c>
-      <c r="G46" s="18">
-        <v>44124</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="5" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E47" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D47)</f>
-        <v>https://www.coursera.org/verify/4XRSLQYDGXHF</v>
+        <v>https://www.coursera.org/verify/8DZVQYMNERJA</v>
       </c>
       <c r="F47" s="16">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G47" s="18">
-        <v>44122</v>
+        <v>44126</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="5" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="E48" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/account/accomplishments/certificate/" &amp; D48)</f>
-        <v>https://www.coursera.org/account/accomplishments/certificate/6KQ8S8U4FGQ5</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D48)</f>
+        <v>https://www.coursera.org/verify/specialization/LGGYURMTBUUG</v>
       </c>
       <c r="F48" s="16">
         <v>1</v>
       </c>
       <c r="G48" s="18">
-        <v>44122</v>
+        <v>44126</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="5" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>103</v>
+        <v>116</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>97</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="E49" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D49)</f>
-        <v>https://www.coursera.org/verify/7JKY6ZQ9D76M</v>
-      </c>
-      <c r="F49" s="7">
-        <v>1</v>
+        <v>https://www.coursera.org/verify/LVBJNAL79BLV</v>
+      </c>
+      <c r="F49" s="16">
+        <v>0.97</v>
       </c>
       <c r="G49" s="18">
-        <v>44112</v>
+        <v>44124</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="5" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E50" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D50)</f>
-        <v>https://www.coursera.org/verify/QWX8PHM4TZUF</v>
-      </c>
-      <c r="F50" s="7">
-        <v>1</v>
-      </c>
-      <c r="G50" s="17">
-        <v>44105</v>
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D50)</f>
+        <v>https://www.coursera.org/verify/specialization/6NXPUFTEK3Z7</v>
+      </c>
+      <c r="F50" s="16">
+        <v>1</v>
+      </c>
+      <c r="G50" s="18">
+        <v>44124</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="5" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="E51" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D51)</f>
-        <v>https://www.coursera.org/verify/ARXP6JVNYNAM</v>
-      </c>
-      <c r="F51" s="7">
-        <v>1</v>
-      </c>
-      <c r="G51" s="17">
-        <v>44105</v>
+        <v>https://www.coursera.org/verify/4XRSLQYDGXHF</v>
+      </c>
+      <c r="F51" s="16">
+        <v>0.98</v>
+      </c>
+      <c r="G51" s="18">
+        <v>44122</v>
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="E52" s="33" t="str">
-        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D52)</f>
-        <v>https://verify.greatlearning.in/UYEYVCWB</v>
-      </c>
-      <c r="F52" s="13">
-        <v>1</v>
-      </c>
-      <c r="G52" s="20">
-        <v>44105</v>
+      <c r="A52" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="E52" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/account/accomplishments/certificate/" &amp; D52)</f>
+        <v>https://www.coursera.org/account/accomplishments/certificate/6KQ8S8U4FGQ5</v>
+      </c>
+      <c r="F52" s="16">
+        <v>1</v>
+      </c>
+      <c r="G52" s="18">
+        <v>44122</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="5" t="s">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E53" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D53)</f>
-        <v>https://www.coursera.org/verify/EUKYBKW2SUXX</v>
+        <v>https://www.coursera.org/verify/7JKY6ZQ9D76M</v>
       </c>
       <c r="F53" s="7">
         <v>1</v>
       </c>
-      <c r="G53" s="17">
-        <v>44104</v>
+      <c r="G53" s="18">
+        <v>44112</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="5" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="E54" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D54)</f>
-        <v>https://www.coursera.org/verify/EUTL7GRT9ZQ4</v>
-      </c>
-      <c r="F54" s="13">
+        <v>https://www.coursera.org/verify/QWX8PHM4TZUF</v>
+      </c>
+      <c r="F54" s="7">
         <v>1</v>
       </c>
       <c r="G54" s="17">
-        <v>44104</v>
+        <v>44105</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="5" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>103</v>
+        <v>123</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E55" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D55)</f>
-        <v>https://www.coursera.org/verify/MX93X95TXB9V</v>
-      </c>
-      <c r="F55" s="13">
+        <v>https://www.coursera.org/verify/ARXP6JVNYNAM</v>
+      </c>
+      <c r="F55" s="7">
         <v>1</v>
       </c>
       <c r="G55" s="17">
-        <v>44080</v>
+        <v>44105</v>
       </c>
     </row>
     <row r="56" spans="1:7">
-      <c r="A56" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E56" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D56)</f>
-        <v>https://www.coursera.org/verify/ERVJF5JMFDRV</v>
+      <c r="A56" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="E56" s="33" t="str">
+        <f>HYPERLINK("https://verify.greatlearning.in/"&amp;D56)</f>
+        <v>https://verify.greatlearning.in/UYEYVCWB</v>
       </c>
       <c r="F56" s="13">
         <v>1</v>
       </c>
-      <c r="G56" s="19">
-        <v>44067</v>
+      <c r="G56" s="20">
+        <v>44105</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="5" t="s">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="F57" s="13">
-        <v>1</v>
-      </c>
-      <c r="G57" s="19">
-        <v>44066</v>
+        <v>97</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E57" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D57)</f>
+        <v>https://www.coursera.org/verify/EUKYBKW2SUXX</v>
+      </c>
+      <c r="F57" s="7">
+        <v>1</v>
+      </c>
+      <c r="G57" s="17">
+        <v>44104</v>
       </c>
     </row>
     <row r="58" spans="1:7">
-      <c r="A58" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>147</v>
-      </c>
-      <c r="D58" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="E58" s="33" t="s">
-        <v>151</v>
+      <c r="A58" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E58" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D58)</f>
+        <v>https://www.coursera.org/verify/EUTL7GRT9ZQ4</v>
       </c>
       <c r="F58" s="13">
         <v>1</v>
       </c>
-      <c r="G58" s="20">
-        <v>44066</v>
+      <c r="G58" s="17">
+        <v>44104</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="5" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="F59" s="7">
-        <v>1</v>
-      </c>
-      <c r="G59" s="19">
-        <v>44066</v>
+        <v>102</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E59" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D59)</f>
+        <v>https://www.coursera.org/verify/MX93X95TXB9V</v>
+      </c>
+      <c r="F59" s="13">
+        <v>1</v>
+      </c>
+      <c r="G59" s="17">
+        <v>44080</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>103</v>
+        <v>138</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>97</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="E60" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D60)</f>
-        <v>https://www.coursera.org/verify/P53AV7SZHJ52</v>
-      </c>
-      <c r="F60" s="7">
-        <v>1</v>
-      </c>
-      <c r="G60" s="17">
-        <v>44063</v>
+        <v>https://www.coursera.org/verify/ERVJF5JMFDRV</v>
+      </c>
+      <c r="F60" s="13">
+        <v>1</v>
+      </c>
+      <c r="G60" s="19">
+        <v>44067</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="E61" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D61)</f>
-        <v>https://www.coursera.org/verify/specialization/FQXP3E6NT3YM</v>
-      </c>
-      <c r="F61" s="7">
-        <v>1</v>
-      </c>
-      <c r="G61" s="17">
-        <v>44063</v>
+        <v>140</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F61" s="13">
+        <v>1</v>
+      </c>
+      <c r="G61" s="19">
+        <v>44066</v>
       </c>
     </row>
     <row r="62" spans="1:7">
-      <c r="A62" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="B62" s="38" t="s">
-        <v>122</v>
-      </c>
-      <c r="C62" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="D62" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="E62" s="47" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D62)</f>
-        <v>https://www.coursera.org/verify/MQ4NMBLXN3G6</v>
-      </c>
-      <c r="F62" s="40">
-        <v>0.97</v>
-      </c>
-      <c r="G62" s="41">
-        <v>44056</v>
+      <c r="A62" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B62" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D62" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="F62" s="13">
+        <v>1</v>
+      </c>
+      <c r="G62" s="20">
+        <v>44066</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="5" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E63" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D63)</f>
-        <v>https://www.coursera.org/verify/UQ5RQLWBRLJA</v>
-      </c>
-      <c r="F63" s="13">
-        <v>0.96</v>
-      </c>
-      <c r="G63" s="17">
-        <v>44055</v>
+        <v>141</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F63" s="7">
+        <v>1</v>
+      </c>
+      <c r="G63" s="19">
+        <v>44066</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C64" s="5" t="s">
-        <v>46</v>
+        <v>148</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D64" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E64" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D64)</f>
+        <v>https://www.coursera.org/verify/P53AV7SZHJ52</v>
+      </c>
+      <c r="F64" s="7">
+        <v>1</v>
+      </c>
+      <c r="G64" s="17">
+        <v>44063</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/specialization/" &amp; D65)</f>
+        <v>https://www.coursera.org/verify/specialization/FQXP3E6NT3YM</v>
+      </c>
+      <c r="F65" s="7">
+        <v>1</v>
+      </c>
+      <c r="G65" s="17">
+        <v>44063</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="C66" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="D66" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="E66" s="47" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D66)</f>
+        <v>https://www.coursera.org/verify/MQ4NMBLXN3G6</v>
+      </c>
+      <c r="F66" s="40">
+        <v>0.97</v>
+      </c>
+      <c r="G66" s="41">
+        <v>44056</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E67" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D67)</f>
+        <v>https://www.coursera.org/verify/UQ5RQLWBRLJA</v>
+      </c>
+      <c r="F67" s="13">
+        <v>0.96</v>
+      </c>
+      <c r="G67" s="17">
+        <v>44055</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="E68" s="6" t="str">
+        <f>HYPERLINK("https://ude.my/"&amp; D68)</f>
+        <v>https://ude.my/UC-57e2fe2c-3570-4bb3-862f-19b05a9b4413</v>
+      </c>
+      <c r="F68" s="13">
+        <v>1</v>
+      </c>
+      <c r="G68" s="17">
+        <v>44054</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E69" s="10" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D69)</f>
+        <v>https://www.coursera.org/verify/HS9S3MQ9U8G5</v>
+      </c>
+      <c r="F69" s="13">
+        <v>1</v>
+      </c>
+      <c r="G69" s="18">
+        <v>44022</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="E70" s="10" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D70)</f>
+        <v>https://www.coursera.org/verify/Z27MPBY34D3J</v>
+      </c>
+      <c r="F70" s="13">
+        <v>1</v>
+      </c>
+      <c r="G70" s="18">
+        <v>44021</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E64" s="6" t="str">
-        <f>HYPERLINK("https://ude.my/"&amp; D64)</f>
-        <v>https://ude.my/UC-57e2fe2c-3570-4bb3-862f-19b05a9b4413</v>
-      </c>
-      <c r="F64" s="13">
-        <v>1</v>
-      </c>
-      <c r="G64" s="17">
-        <v>44054</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7">
-      <c r="A65" s="12" t="s">
+      <c r="E71" s="10" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D71)</f>
+        <v>https://www.coursera.org/verify/L4NCNJMVFQPU</v>
+      </c>
+      <c r="F71" s="13">
+        <v>1</v>
+      </c>
+      <c r="G71" s="18">
+        <v>44013</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B72" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E72" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D72)</f>
+        <v>https://www.hackerrank.com/certificates/867DAFFABDA4</v>
+      </c>
+      <c r="F72" s="11">
+        <v>1</v>
+      </c>
+      <c r="G72" s="17">
+        <v>44004</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E73" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D73)</f>
+        <v>https://www.hackerrank.com/certificates/2766975846A6</v>
+      </c>
+      <c r="F73" s="11">
+        <v>1</v>
+      </c>
+      <c r="G73" s="17">
+        <v>44003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E74" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D74)</f>
+        <v>https://www.hackerrank.com/certificates/1140C95B9B14</v>
+      </c>
+      <c r="F74" s="61">
+        <v>1</v>
+      </c>
+      <c r="G74" s="17">
+        <v>44003</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E75" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D75)</f>
+        <v>https://www.coursera.org/verify/WG7CRBWGK8FW</v>
+      </c>
+      <c r="F75" s="16">
+        <v>1</v>
+      </c>
+      <c r="G75" s="17">
+        <v>43999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C65" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="E65" s="10" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D65)</f>
-        <v>https://www.coursera.org/verify/HS9S3MQ9U8G5</v>
-      </c>
-      <c r="F65" s="13">
-        <v>1</v>
-      </c>
-      <c r="G65" s="18">
-        <v>44022</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7">
-      <c r="A66" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="B66" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E66" s="10" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D66)</f>
-        <v>https://www.coursera.org/verify/Z27MPBY34D3J</v>
-      </c>
-      <c r="F66" s="13">
-        <v>1</v>
-      </c>
-      <c r="G66" s="18">
-        <v>44021</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7">
-      <c r="A67" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="B67" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="E67" s="10" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D67)</f>
-        <v>https://www.coursera.org/verify/L4NCNJMVFQPU</v>
-      </c>
-      <c r="F67" s="13">
-        <v>1</v>
-      </c>
-      <c r="G67" s="18">
-        <v>44013</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7">
-      <c r="A68" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B68" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E68" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D68)</f>
-        <v>https://www.hackerrank.com/certificates/867DAFFABDA4</v>
-      </c>
-      <c r="F68" s="11">
-        <v>1</v>
-      </c>
-      <c r="G68" s="17">
-        <v>44004</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7">
-      <c r="A69" s="2" t="s">
+      <c r="C76" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D76" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D69" s="2" t="s">
+      <c r="E76" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D76)</f>
+        <v>https://www.coursera.org/verify/L5XQHDFRBG5S</v>
+      </c>
+      <c r="F76" s="7">
+        <v>0.94</v>
+      </c>
+      <c r="G76" s="17">
+        <v>43995</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="E69" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D69)</f>
-        <v>https://www.hackerrank.com/certificates/2766975846A6</v>
-      </c>
-      <c r="F69" s="11">
-        <v>1</v>
-      </c>
-      <c r="G69" s="17">
-        <v>44003</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7">
-      <c r="A70" s="2" t="s">
+      <c r="B77" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D70" s="2" t="s">
+      <c r="C77" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D77" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E70" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.hackerrank.com/certificates/" &amp; D70)</f>
-        <v>https://www.hackerrank.com/certificates/1140C95B9B14</v>
-      </c>
-      <c r="F70" s="62">
-        <v>1</v>
-      </c>
-      <c r="G70" s="17">
-        <v>44003</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7">
-      <c r="A71" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D71" s="5" t="s">
+      <c r="E77" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D77)</f>
+        <v>https://www.coursera.org/verify/F6ASNEAAYVGZ</v>
+      </c>
+      <c r="F77" s="7">
+        <v>0.94</v>
+      </c>
+      <c r="G77" s="17">
+        <v>43987</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="E71" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D71)</f>
-        <v>https://www.coursera.org/verify/WG7CRBWGK8FW</v>
-      </c>
-      <c r="F71" s="16">
-        <v>1</v>
-      </c>
-      <c r="G71" s="17">
-        <v>43999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7">
-      <c r="A72" s="5" t="s">
+      <c r="B78" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D78" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E72" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D72)</f>
-        <v>https://www.coursera.org/verify/L5XQHDFRBG5S</v>
-      </c>
-      <c r="F72" s="7">
-        <v>0.94</v>
-      </c>
-      <c r="G72" s="17">
-        <v>43995</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7">
-      <c r="A73" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="E73" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D73)</f>
-        <v>https://www.coursera.org/verify/F6ASNEAAYVGZ</v>
-      </c>
-      <c r="F73" s="7">
-        <v>0.94</v>
-      </c>
-      <c r="G73" s="17">
-        <v>43987</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7">
-      <c r="A74" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E74" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D74)</f>
-        <v>https://www.coursera.org/verify/3W45QQBKACKZ</v>
-      </c>
-      <c r="F74" s="7">
-        <v>1</v>
-      </c>
-      <c r="G74" s="17">
-        <v>43986</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7">
-      <c r="A75" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="E75" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F75" s="11">
-        <v>1</v>
-      </c>
-      <c r="G75" s="18">
-        <v>43984</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7">
-      <c r="A76" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="B76" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="E76" s="10" t="s">
-        <v>190</v>
-      </c>
-      <c r="F76" s="11">
-        <v>0.9</v>
-      </c>
-      <c r="G76" s="18">
-        <v>43983</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7">
-      <c r="A77" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C77" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="E77" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="F77" s="11">
-        <v>0.8</v>
-      </c>
-      <c r="G77" s="18">
-        <v>43983</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7">
-      <c r="A78" s="58" t="s">
-        <v>194</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>196</v>
       </c>
       <c r="E78" s="3" t="str">
         <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D78)</f>
+        <v>https://www.coursera.org/verify/3W45QQBKACKZ</v>
+      </c>
+      <c r="F78" s="7">
+        <v>1</v>
+      </c>
+      <c r="G78" s="17">
+        <v>43986</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="F79" s="11">
+        <v>1</v>
+      </c>
+      <c r="G79" s="18">
+        <v>43984</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B80" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="F80" s="11">
+        <v>0.9</v>
+      </c>
+      <c r="G80" s="18">
+        <v>43983</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C81" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F81" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="G81" s="18">
+        <v>43983</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="E82" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D82)</f>
         <v>https://www.coursera.org/verify/ZM9BMYXLN942</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F82" s="7">
         <v>0.83</v>
       </c>
-      <c r="G78" s="17">
+      <c r="G82" s="17">
         <v>43983</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
-      <c r="A79" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E79" s="3" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D79)</f>
+    <row r="83" spans="1:7">
+      <c r="A83" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E83" s="3" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D83)</f>
         <v>https://www.coursera.org/verify/FKLHXG2L7ZV2</v>
       </c>
-      <c r="F79" s="4">
-        <v>1</v>
-      </c>
-      <c r="G79" s="17">
+      <c r="F83" s="4">
+        <v>1</v>
+      </c>
+      <c r="G83" s="17">
         <v>43978</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7">
-      <c r="A80" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="B80" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="E80" s="10" t="str">
-        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D80)</f>
-        <v>https://www.coursera.org/verify/LSGX9WZD2829</v>
-      </c>
-      <c r="F80" s="11">
-        <v>0.98</v>
-      </c>
-      <c r="G80" s="18">
-        <v>43968</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7">
-      <c r="A81" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F81" s="4">
-        <v>1</v>
-      </c>
-      <c r="G81" s="17">
-        <v>43965</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7">
-      <c r="A82" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B82" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="F82" s="11">
-        <v>1</v>
-      </c>
-      <c r="G82" s="18">
-        <v>43956</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7">
-      <c r="A83" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="F83" s="11">
-        <v>1</v>
-      </c>
-      <c r="G83" s="18">
-        <v>43953</v>
       </c>
     </row>
     <row r="84" spans="1:7">
       <c r="A84" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C84" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E84" s="10" t="str">
+        <f xml:space="preserve"> HYPERLINK("https://www.coursera.org/verify/" &amp; D84)</f>
+        <v>https://www.coursera.org/verify/LSGX9WZD2829</v>
+      </c>
+      <c r="F84" s="11">
+        <v>0.98</v>
+      </c>
+      <c r="G84" s="18">
+        <v>43968</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F85" s="4">
+        <v>1</v>
+      </c>
+      <c r="G85" s="17">
+        <v>43965</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="C86" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F86" s="11">
+        <v>1</v>
+      </c>
+      <c r="G86" s="18">
+        <v>43956</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="C87" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F87" s="11">
+        <v>1</v>
+      </c>
+      <c r="G87" s="18">
+        <v>43953</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C88" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F88" s="11">
+        <v>1</v>
+      </c>
+      <c r="G88" s="18">
+        <v>43871</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F89" s="11">
+        <v>1</v>
+      </c>
+      <c r="G89" s="18">
+        <v>43551</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" s="56" t="s">
         <v>213</v>
       </c>
-      <c r="B84" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D84" s="9" t="s">
+      <c r="B90" s="56" t="s">
         <v>214</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="C90" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="D90" s="56" t="s">
         <v>215</v>
       </c>
-      <c r="F84" s="11">
-        <v>1</v>
-      </c>
-      <c r="G84" s="18">
-        <v>43871</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7">
-      <c r="A85" s="9" t="s">
+      <c r="E90" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="B85" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="E85" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="F85" s="11">
-        <v>1</v>
-      </c>
-      <c r="G85" s="18">
-        <v>43551</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7">
-      <c r="A86" s="57" t="s">
-        <v>219</v>
-      </c>
-      <c r="B86" s="57" t="s">
-        <v>220</v>
-      </c>
-      <c r="C86" s="57" t="s">
-        <v>220</v>
-      </c>
-      <c r="D86" s="57" t="s">
-        <v>221</v>
-      </c>
-      <c r="E86" s="60" t="s">
-        <v>222</v>
-      </c>
-      <c r="F86" s="61">
-        <v>1</v>
-      </c>
-      <c r="G86" s="63">
+      <c r="F90" s="60">
+        <v>1</v>
+      </c>
+      <c r="G90" s="62">
         <v>43549</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G86" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G86">
-      <sortCondition descending="1" ref="G1:G86"/>
+  <autoFilter ref="A1:G90" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G90">
+      <sortCondition descending="1" ref="G1:G90"/>
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="E86" r:id="rId1" xr:uid="{6C0DBD8A-06FB-4276-97CC-44F7D2A620D3}"/>
-    <hyperlink ref="E85" r:id="rId2" xr:uid="{A3AA2B4E-A070-4264-BAD0-50B1BD9F111B}"/>
-    <hyperlink ref="E84" r:id="rId3" xr:uid="{9B48E280-22D3-4A9E-8D60-7F69F560315A}"/>
-    <hyperlink ref="E82" r:id="rId4" xr:uid="{A1888FFC-F836-43B1-ACCE-D7ED9F0B270F}"/>
-    <hyperlink ref="E83" r:id="rId5" xr:uid="{1D430177-A56E-4567-8FAC-5E8420D918CC}"/>
-    <hyperlink ref="E80" r:id="rId6" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{1F5AE59F-A263-4228-9C7E-266BAD69AD6D}"/>
-    <hyperlink ref="E81" r:id="rId7" xr:uid="{CE2198E5-2DEE-4B00-8F0C-17EA31FD42CF}"/>
-    <hyperlink ref="E75" r:id="rId8" xr:uid="{D9C0C981-CB38-4235-A77B-7B73A8D1355B}"/>
-    <hyperlink ref="E76" r:id="rId9" xr:uid="{256B4442-C33A-484D-A51A-03B0A68C0D1A}"/>
-    <hyperlink ref="E77" r:id="rId10" xr:uid="{11511F3E-24A6-40DC-8710-D6F763ABC7D0}"/>
-    <hyperlink ref="E69" r:id="rId11" display="https://www.hackerrank.com/certificates/2766975846a6" xr:uid="{23538072-30C4-4325-A871-9979C940114B}"/>
-    <hyperlink ref="E70" r:id="rId12" display="https://www.hackerrank.com/certificates/1140c95b9b14" xr:uid="{92658253-7FDE-4177-9BB5-57ABBEC11707}"/>
-    <hyperlink ref="E68" r:id="rId13" display="https://www.hackerrank.com/certificates/867daffabda4" xr:uid="{760F6237-ED74-4C76-921F-A92DB49AA851}"/>
-    <hyperlink ref="E41" r:id="rId14" xr:uid="{BE109821-CCDD-4A04-981A-9F6EFC5839F3}"/>
-    <hyperlink ref="E39" r:id="rId15" display="https://www.hackerrank.com/certificates/3af4ddb28fab" xr:uid="{193C03FB-8BC6-4219-AB14-ECE3411E93FC}"/>
-    <hyperlink ref="E36" r:id="rId16" xr:uid="{C4C48324-FD2D-4D60-97F7-1C543194CDA1}"/>
-    <hyperlink ref="E35" r:id="rId17" xr:uid="{24CD5469-5A68-4595-8905-E3195BAA26D6}"/>
-    <hyperlink ref="E34" r:id="rId18" display="https://www.hackerrank.com/certificates/6730cf1d0f21" xr:uid="{4E5A9F5D-377D-4813-82DA-653909A03F55}"/>
-    <hyperlink ref="E33" r:id="rId19" xr:uid="{13330E2D-247C-4D68-B3A4-25AEC2481299}"/>
-    <hyperlink ref="E14" r:id="rId20" xr:uid="{104CE576-4E8E-4A67-852D-469446BC152A}"/>
-    <hyperlink ref="E11" r:id="rId21" xr:uid="{F5B1676B-40C2-41E4-8A7C-EE0DDF96B5AB}"/>
-    <hyperlink ref="E12" r:id="rId22" xr:uid="{CF1353C0-1B68-45EB-B9D3-B3815B4819F9}"/>
-    <hyperlink ref="E13" r:id="rId23" xr:uid="{C08302DF-FF6D-47C0-8C56-3AB13A011040}"/>
-    <hyperlink ref="E15" r:id="rId24" display="https://olympus1.greatlearning.in/course_certificate/UAEGKOSB" xr:uid="{D327F964-4247-480C-ABF2-CE1C58A5C248}"/>
-    <hyperlink ref="E19" r:id="rId25" xr:uid="{899ABF8F-A4FE-4A5E-81D4-FDAA431DAB0E}"/>
-    <hyperlink ref="E24" r:id="rId26" display="https://www.hackerrank.com/certificates/cf58231a440f" xr:uid="{DE2CBB3E-53B4-4A72-B17A-95F8DC50A680}"/>
-    <hyperlink ref="E27" r:id="rId27" display="https://verify.greatlearning.in/SSMRYOWJ" xr:uid="{5873F399-7F29-4029-A2AF-C59477D7EEFA}"/>
-    <hyperlink ref="E28" r:id="rId28" display="https://verify.greatlearning.in/ZYQTXTJA" xr:uid="{9CE1A66B-C3BE-475F-9AAC-35D820A2B426}"/>
-    <hyperlink ref="E29" r:id="rId29" display="https://verify.greatlearning.in/GQGRZFQQ" xr:uid="{5442A54E-DEC1-418C-88C0-D3881C3E7DF7}"/>
-    <hyperlink ref="E25" r:id="rId30" display="https://www.hackerrank.com/certificates/4490b4a0e606" xr:uid="{03797E5A-D7A7-48A4-A1B4-62A5C7C463AF}"/>
-    <hyperlink ref="E26" r:id="rId31" display="https://www.hackerrank.com/certificates/fdeeaad81310" xr:uid="{0492AAD8-A54A-4838-943A-8F8C8C981536}"/>
-    <hyperlink ref="E31" r:id="rId32" display="https://www.hackerrank.com/certificates/1cadc360a79d" xr:uid="{D163DA80-AE56-4D17-80D1-BCE62B9B0E77}"/>
-    <hyperlink ref="E37" r:id="rId33" xr:uid="{7EB46669-C518-425D-8A3E-395F05BE96F4}"/>
-    <hyperlink ref="E57" r:id="rId34" xr:uid="{E604A0FD-1B8B-4069-A5D9-749A14F9519E}"/>
-    <hyperlink ref="E58" r:id="rId35" xr:uid="{6D72DCB3-71D9-4096-B636-A24037DEC0A0}"/>
-    <hyperlink ref="E59" r:id="rId36" xr:uid="{F48B074D-BE93-4758-BDD0-50BF937B211E}"/>
-    <hyperlink ref="E10" r:id="rId37" xr:uid="{7F8992C5-905E-4B72-82BE-676D324D1D17}"/>
-    <hyperlink ref="E79" r:id="rId38" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{C875791B-2744-4F5C-9948-8B038AB7B795}"/>
-    <hyperlink ref="E29:E42" r:id="rId39" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{CE0B26B0-E940-4BD5-8F74-8D28A4F3B13A}"/>
-    <hyperlink ref="E38" r:id="rId40" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{5152B189-9CFA-4B7A-842F-93D4B5F53177}"/>
-    <hyperlink ref="E56" r:id="rId41" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{5C171493-E45D-436D-968B-6A7D6CED71CA}"/>
-    <hyperlink ref="E16" r:id="rId42" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{CC465E8A-1F75-432D-9DC6-368FD314B682}"/>
-    <hyperlink ref="E9:E10" r:id="rId43" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{C55AB7BE-0BE1-4CE1-8CFE-C0E7B2B0BA28}"/>
-    <hyperlink ref="E12:E15" r:id="rId44" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{549C4CBA-43AF-4870-BE36-8D1CBC3CFD71}"/>
-    <hyperlink ref="E32" r:id="rId45" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{53B8A539-1C54-4D29-828E-465373C8A2C4}"/>
-    <hyperlink ref="E64" r:id="rId46" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{6D2FD0D9-7715-4D27-986B-9CBDCC24BC65}"/>
-    <hyperlink ref="E9" r:id="rId47" xr:uid="{699CE3D0-7418-4EFB-9798-81677CCAC0DE}"/>
-    <hyperlink ref="E8" r:id="rId48" display="https://www.hackerrank.com/certificates/eafe133d26dc" xr:uid="{3748E750-A80A-4402-BC5F-803B16F27441}"/>
-    <hyperlink ref="E5" r:id="rId49" xr:uid="{59D89928-3553-4495-8CD7-92EBC3B422E3}"/>
-    <hyperlink ref="E4" r:id="rId50" xr:uid="{90A10946-4B5C-4200-83CE-B2047CBD914F}"/>
-    <hyperlink ref="E3" r:id="rId51" xr:uid="{3280A986-162F-4133-9109-1EE526FB0D39}"/>
-    <hyperlink ref="E2" r:id="rId52" xr:uid="{0A52842B-3BD1-4EDE-ABBA-FF846F26BE9D}"/>
+    <hyperlink ref="E90" r:id="rId1" xr:uid="{6C0DBD8A-06FB-4276-97CC-44F7D2A620D3}"/>
+    <hyperlink ref="E89" r:id="rId2" xr:uid="{A3AA2B4E-A070-4264-BAD0-50B1BD9F111B}"/>
+    <hyperlink ref="E88" r:id="rId3" xr:uid="{9B48E280-22D3-4A9E-8D60-7F69F560315A}"/>
+    <hyperlink ref="E86" r:id="rId4" xr:uid="{A1888FFC-F836-43B1-ACCE-D7ED9F0B270F}"/>
+    <hyperlink ref="E87" r:id="rId5" xr:uid="{1D430177-A56E-4567-8FAC-5E8420D918CC}"/>
+    <hyperlink ref="E84" r:id="rId6" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{1F5AE59F-A263-4228-9C7E-266BAD69AD6D}"/>
+    <hyperlink ref="E85" r:id="rId7" xr:uid="{CE2198E5-2DEE-4B00-8F0C-17EA31FD42CF}"/>
+    <hyperlink ref="E79" r:id="rId8" xr:uid="{D9C0C981-CB38-4235-A77B-7B73A8D1355B}"/>
+    <hyperlink ref="E80" r:id="rId9" xr:uid="{256B4442-C33A-484D-A51A-03B0A68C0D1A}"/>
+    <hyperlink ref="E81" r:id="rId10" xr:uid="{11511F3E-24A6-40DC-8710-D6F763ABC7D0}"/>
+    <hyperlink ref="E73" r:id="rId11" display="https://www.hackerrank.com/certificates/2766975846a6" xr:uid="{23538072-30C4-4325-A871-9979C940114B}"/>
+    <hyperlink ref="E74" r:id="rId12" display="https://www.hackerrank.com/certificates/1140c95b9b14" xr:uid="{92658253-7FDE-4177-9BB5-57ABBEC11707}"/>
+    <hyperlink ref="E72" r:id="rId13" display="https://www.hackerrank.com/certificates/867daffabda4" xr:uid="{760F6237-ED74-4C76-921F-A92DB49AA851}"/>
+    <hyperlink ref="E45" r:id="rId14" xr:uid="{BE109821-CCDD-4A04-981A-9F6EFC5839F3}"/>
+    <hyperlink ref="E43" r:id="rId15" display="https://www.hackerrank.com/certificates/3af4ddb28fab" xr:uid="{193C03FB-8BC6-4219-AB14-ECE3411E93FC}"/>
+    <hyperlink ref="E40" r:id="rId16" xr:uid="{C4C48324-FD2D-4D60-97F7-1C543194CDA1}"/>
+    <hyperlink ref="E39" r:id="rId17" xr:uid="{24CD5469-5A68-4595-8905-E3195BAA26D6}"/>
+    <hyperlink ref="E38" r:id="rId18" display="https://www.hackerrank.com/certificates/6730cf1d0f21" xr:uid="{4E5A9F5D-377D-4813-82DA-653909A03F55}"/>
+    <hyperlink ref="E37" r:id="rId19" xr:uid="{13330E2D-247C-4D68-B3A4-25AEC2481299}"/>
+    <hyperlink ref="E18" r:id="rId20" xr:uid="{104CE576-4E8E-4A67-852D-469446BC152A}"/>
+    <hyperlink ref="E15" r:id="rId21" xr:uid="{F5B1676B-40C2-41E4-8A7C-EE0DDF96B5AB}"/>
+    <hyperlink ref="E16" r:id="rId22" xr:uid="{CF1353C0-1B68-45EB-B9D3-B3815B4819F9}"/>
+    <hyperlink ref="E17" r:id="rId23" xr:uid="{C08302DF-FF6D-47C0-8C56-3AB13A011040}"/>
+    <hyperlink ref="E19" r:id="rId24" display="https://olympus1.greatlearning.in/course_certificate/UAEGKOSB" xr:uid="{D327F964-4247-480C-ABF2-CE1C58A5C248}"/>
+    <hyperlink ref="E23" r:id="rId25" xr:uid="{899ABF8F-A4FE-4A5E-81D4-FDAA431DAB0E}"/>
+    <hyperlink ref="E28" r:id="rId26" display="https://www.hackerrank.com/certificates/cf58231a440f" xr:uid="{DE2CBB3E-53B4-4A72-B17A-95F8DC50A680}"/>
+    <hyperlink ref="E31" r:id="rId27" display="https://verify.greatlearning.in/SSMRYOWJ" xr:uid="{5873F399-7F29-4029-A2AF-C59477D7EEFA}"/>
+    <hyperlink ref="E32" r:id="rId28" display="https://verify.greatlearning.in/ZYQTXTJA" xr:uid="{9CE1A66B-C3BE-475F-9AAC-35D820A2B426}"/>
+    <hyperlink ref="E33" r:id="rId29" display="https://verify.greatlearning.in/GQGRZFQQ" xr:uid="{5442A54E-DEC1-418C-88C0-D3881C3E7DF7}"/>
+    <hyperlink ref="E29" r:id="rId30" display="https://www.hackerrank.com/certificates/4490b4a0e606" xr:uid="{03797E5A-D7A7-48A4-A1B4-62A5C7C463AF}"/>
+    <hyperlink ref="E30" r:id="rId31" display="https://www.hackerrank.com/certificates/fdeeaad81310" xr:uid="{0492AAD8-A54A-4838-943A-8F8C8C981536}"/>
+    <hyperlink ref="E35" r:id="rId32" display="https://www.hackerrank.com/certificates/1cadc360a79d" xr:uid="{D163DA80-AE56-4D17-80D1-BCE62B9B0E77}"/>
+    <hyperlink ref="E41" r:id="rId33" xr:uid="{7EB46669-C518-425D-8A3E-395F05BE96F4}"/>
+    <hyperlink ref="E61" r:id="rId34" xr:uid="{E604A0FD-1B8B-4069-A5D9-749A14F9519E}"/>
+    <hyperlink ref="E62" r:id="rId35" xr:uid="{6D72DCB3-71D9-4096-B636-A24037DEC0A0}"/>
+    <hyperlink ref="E63" r:id="rId36" xr:uid="{F48B074D-BE93-4758-BDD0-50BF937B211E}"/>
+    <hyperlink ref="E14" r:id="rId37" xr:uid="{7F8992C5-905E-4B72-82BE-676D324D1D17}"/>
+    <hyperlink ref="E83" r:id="rId38" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{C875791B-2744-4F5C-9948-8B038AB7B795}"/>
+    <hyperlink ref="E33:E46" r:id="rId39" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{CE0B26B0-E940-4BD5-8F74-8D28A4F3B13A}"/>
+    <hyperlink ref="E42" r:id="rId40" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{5152B189-9CFA-4B7A-842F-93D4B5F53177}"/>
+    <hyperlink ref="E60" r:id="rId41" display="https://www.coursera.org/verify/LSGX9WZD2829" xr:uid="{5C171493-E45D-436D-968B-6A7D6CED71CA}"/>
+    <hyperlink ref="E20" r:id="rId42" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{CC465E8A-1F75-432D-9DC6-368FD314B682}"/>
+    <hyperlink ref="E13:E14" r:id="rId43" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{C55AB7BE-0BE1-4CE1-8CFE-C0E7B2B0BA28}"/>
+    <hyperlink ref="E16:E19" r:id="rId44" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{549C4CBA-43AF-4870-BE36-8D1CBC3CFD71}"/>
+    <hyperlink ref="E36" r:id="rId45" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{53B8A539-1C54-4D29-828E-465373C8A2C4}"/>
+    <hyperlink ref="E68" r:id="rId46" display="https://www.udemy.com/certificate/UC-cba24dc1-e21d-4c7c-b5b3-1cd55995d707/" xr:uid="{6D2FD0D9-7715-4D27-986B-9CBDCC24BC65}"/>
+    <hyperlink ref="E13" r:id="rId47" xr:uid="{699CE3D0-7418-4EFB-9798-81677CCAC0DE}"/>
+    <hyperlink ref="E12" r:id="rId48" display="https://www.hackerrank.com/certificates/eafe133d26dc" xr:uid="{3748E750-A80A-4402-BC5F-803B16F27441}"/>
+    <hyperlink ref="E9" r:id="rId49" xr:uid="{59D89928-3553-4495-8CD7-92EBC3B422E3}"/>
+    <hyperlink ref="E8" r:id="rId50" xr:uid="{90A10946-4B5C-4200-83CE-B2047CBD914F}"/>
+    <hyperlink ref="E7" r:id="rId51" xr:uid="{3280A986-162F-4133-9109-1EE526FB0D39}"/>
+    <hyperlink ref="E4" r:id="rId52" xr:uid="{0A52842B-3BD1-4EDE-ABBA-FF846F26BE9D}"/>
+    <hyperlink ref="E5" r:id="rId53" xr:uid="{72F319DE-49C4-4B73-AAE6-722324F72419}"/>
+    <hyperlink ref="E6" r:id="rId54" xr:uid="{38912FCD-0B08-47AC-80ED-1792AC4D00DB}"/>
+    <hyperlink ref="E3" r:id="rId55" xr:uid="{2D40B2B0-49CE-4179-B7BF-30B92B7BAF96}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3753,25 +3898,25 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="G1" s="25" t="s">
         <v>223</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>229</v>
       </c>
       <c r="H1" s="23" t="s">
         <v>3</v>
@@ -3782,46 +3927,46 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F2" s="26">
         <v>44652</v>
       </c>
       <c r="G2" s="26" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="5" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" s="24" t="s">
         <v>231</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>233</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>238</v>
       </c>
       <c r="F3" s="26">
         <v>44470</v>
@@ -3830,25 +3975,25 @@
         <v>44651</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="24" t="s">
         <v>230</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>237</v>
-      </c>
       <c r="D4" s="24" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F4" s="19">
         <v>44378</v>
@@ -3857,25 +4002,25 @@
         <v>44469</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" s="32" customFormat="1">
       <c r="A5" s="5" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F5" s="19">
         <v>44263</v>
@@ -3884,25 +4029,25 @@
         <v>44377</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="57.6">
       <c r="A6" s="27" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F6" s="30">
         <v>44137</v>
@@ -3911,27 +4056,27 @@
         <v>44200</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I6" s="31" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="5" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F7" s="19">
         <v>44136</v>
@@ -3940,27 +4085,27 @@
         <v>44166</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="5" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F8" s="19">
         <v>44105</v>
@@ -3969,27 +4114,27 @@
         <v>44136</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="5" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F9" s="26">
         <v>43432</v>
@@ -3998,10 +4143,10 @@
         <v>43442</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -4055,7 +4200,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718451B2-E12D-4ABD-B26C-5975AED3964E}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -4064,15 +4209,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="36" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B2" s="7">
         <v>0.9</v>
@@ -4080,23 +4225,23 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="5" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="B3" s="7">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>259</v>
+        <v>344</v>
       </c>
       <c r="B4" s="7">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B5" s="7">
         <v>0.8</v>
@@ -4104,7 +4249,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="5" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B6" s="7">
         <v>0.8</v>
@@ -4112,7 +4257,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="B7" s="7">
         <v>0.8</v>
@@ -4120,7 +4265,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B8" s="7">
         <v>0.8</v>
@@ -4128,7 +4273,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="B9" s="7">
         <v>0.8</v>
@@ -4136,7 +4281,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B10" s="7">
         <v>0.8</v>
@@ -4144,7 +4289,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="B11" s="7">
         <v>0.7</v>
@@ -4152,7 +4297,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="B12" s="7">
         <v>0.7</v>
@@ -4160,7 +4305,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B13" s="7">
         <v>0.7</v>
@@ -4168,15 +4313,15 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="B14" s="7">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B15" s="7">
         <v>0.6</v>
@@ -4184,7 +4329,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="5" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="B16" s="7">
         <v>0.6</v>
@@ -4192,7 +4337,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B17" s="7">
         <v>0.6</v>
@@ -4200,7 +4345,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="5" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="B18" s="7">
         <v>0.6</v>
@@ -4208,7 +4353,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="5" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="B19" s="7">
         <v>0.6</v>
@@ -4216,7 +4361,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="5" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="B20" s="7">
         <v>0.6</v>
@@ -4224,23 +4369,15 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="5" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B21" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B22" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:B21" xr:uid="{718451B2-E12D-4ABD-B26C-5975AED3964E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B22">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B21">
       <sortCondition descending="1" ref="B1:B21"/>
     </sortState>
   </autoFilter>
@@ -4264,195 +4401,195 @@
         <v>0</v>
       </c>
       <c r="B1" s="37" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C1" s="37" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="D1" s="37" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="5" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="5" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="5" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="5" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="5" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="5" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="5" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -4476,12 +4613,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4702,15 +4836,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E4A532-34F4-4909-9773-2D1B4D74CA0C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F92213D-1611-4A06-8F7F-2A2F3FD54BB4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4735,10 +4873,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F92213D-1611-4A06-8F7F-2A2F3FD54BB4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5E4A532-34F4-4909-9773-2D1B4D74CA0C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>